--- a/photo_manual.xlsx
+++ b/photo_manual.xlsx
@@ -65,13 +65,13 @@
     <t>Батончики и шоколад</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/059.png</t>
+    <t>059.png</t>
   </si>
   <si>
     <t>Акконд батончик Отломи 33г/16 (6) Маленький</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/050.png</t>
+    <t>050.png</t>
   </si>
   <si>
     <t>Акконд батончик Отломи 48г/22 Большой</t>
@@ -83,25 +83,25 @@
     <t>Конфеты и печенье</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_125.png</t>
+    <t>Screenshot_125.png</t>
   </si>
   <si>
     <t>Акконд вафли фас. Хуторок 250г/6</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_122.png</t>
+    <t>Screenshot_122.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Вита+Мини Мята-Ментол 1/4кг</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_102.png</t>
+    <t>Screenshot_102.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель жевательная Капелька ассорти 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_108.png</t>
+    <t>Screenshot_108.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель жевательная Капелька со вкусом апельсина 1/5</t>
@@ -110,13 +110,13 @@
     <t>Акконд вес. карамель жевательная Капелька со вкусом клубники 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_106.png</t>
+    <t>Screenshot_106.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Ликёрная 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_115.png</t>
+    <t>Screenshot_115.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Ликёрная микс 1/4</t>
@@ -125,49 +125,49 @@
     <t>Акконд вес. карамель Ликёрная со вкусом Амаретто 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_114.png</t>
+    <t>Screenshot_114.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Ликёрная со вкусом Бейлиз 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_116.png</t>
+    <t>Screenshot_116.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Лимонадия со вкусом Тархуна карамель 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_99.png</t>
+    <t>Screenshot_99.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Молочная речка 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_117.png</t>
+    <t>Screenshot_117.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рози Блюз COFFEE 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_179.png</t>
+    <t>Screenshot_179.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рози Блюз MILK 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_181.png</t>
+    <t>Screenshot_181.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рози Блюз дюшес 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_183.png</t>
+    <t>Screenshot_183.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рози Блюз Кола 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_180.png</t>
+    <t>Screenshot_180.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рози Блюз лимонадный микс 1/4</t>
@@ -176,91 +176,91 @@
     <t>Акконд вес. карамель Рози Блюз со вкусом Малины и Сливок 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_182.png</t>
+    <t>Screenshot_182.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рыжуха 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_118.png</t>
+    <t>Screenshot_118.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Рыжуха со вкусом кофе и сливок 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_119.png</t>
+    <t>Screenshot_119.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Эвкалипт-Имбирь 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_112.png</t>
+    <t>Screenshot_112.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Эвкалипт-Ментол 1/4 + (флоу-пак)</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_188.png</t>
+    <t>Screenshot_188.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Эвкалипт-Ментол 1/5 + перекрут</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_113.png</t>
+    <t>Screenshot_113.png</t>
   </si>
   <si>
     <t>Акконд вес. карамель Эвкалипт-Ментол 1/5 экстра</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_110.png</t>
+    <t>Screenshot_110.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Адель с цельн.миндалем 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/089.png</t>
+    <t>089.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Адель с цельн.миндалем и вишней 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/090.png</t>
+    <t>090.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Аккондовская КАРТОШКА Pralineo 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_189.png</t>
+    <t>Screenshot_189.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Бабочка 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_84.png</t>
+    <t>Screenshot_84.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Батончик Акконд 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_28.png</t>
+    <t>Screenshot_28.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Бравер с кофейной начинкой 1/6</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_190.png</t>
+    <t>Screenshot_190.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Бравер с ореховой начинкой 1/6</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_191.png</t>
+    <t>Screenshot_191.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Бравер с шоколадной начинкой 1/6</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_192.png</t>
+    <t>Screenshot_192.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты вафли Хуторок 1/3</t>
@@ -269,55 +269,55 @@
     <t>Акконд вес. конфеты десерт Мини Рулик вишнёвый 2кг УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/033.png</t>
+    <t>033.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты десерт Мини Рулик карам. молоко 2кг УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/031.png</t>
+    <t>031.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты десерт Мини Рулик карам. молоко глазир 2кг УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/032.png</t>
+    <t>032.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты желейные Отважный комарик со вкусом Манго-Апельсин 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_71.png</t>
+    <t>Screenshot_71.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Зачарованные MEGA 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_193.png</t>
+    <t>Screenshot_193.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Зернушка 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_32.png</t>
+    <t>Screenshot_32.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Лапки-Царапки 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_34.png</t>
+    <t>Screenshot_34.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Ломтишка Клубника десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_194.png</t>
+    <t>Screenshot_194.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Львиное сердце кокос 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_195.png</t>
+    <t>Screenshot_195.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Молочная речка горячий шоколад в глазури 1/3</t>
@@ -326,152 +326,151 @@
     <t>Акконд вес. конфеты Нямик молочные 1/4кг</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_196.png</t>
+    <t>Screenshot_196.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Отломи  Тоффи1/4кг</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_197.png</t>
+    <t>Screenshot_197.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Отломи с кокосом 1/2кг УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_198.png</t>
+    <t>Screenshot_198.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты пастила Аккондовская макси со вкусом Ванили 1/4 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_199.png</t>
+    <t>Screenshot_199.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Слимо Стик с арахисом 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_200.png</t>
+    <t>Screenshot_200.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Слимо Тоффи с арахисом и изюмом 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_91.png</t>
+    <t>Screenshot_91.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Слимо хрустящие с миндалём 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_89.png</t>
+    <t>Screenshot_89.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты ТРИО с печеньем , карамелью и начинкой пломбир  1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/096.png</t>
+    <t>096.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Шоконатка 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_22.png</t>
+    <t>Screenshot_22.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Шоконатка с арахисом 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_23.png</t>
+    <t>Screenshot_23.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Шоконатка трюфель 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_24.png</t>
+    <t>Screenshot_24.png</t>
   </si>
   <si>
     <t>Акконд крекер вес. АККОНДОВСКИЙ с солью 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_172.png</t>
+    <t>Screenshot_172.png</t>
   </si>
   <si>
     <t>Акконд крекер вес. АККОНДОВСКИЙ ФИТСИ 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_201.png</t>
+    <t>Screenshot_201.png</t>
   </si>
   <si>
     <t>Акконд Крекер с солью 190г/20</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_202.png</t>
+    <t>Screenshot_202.png</t>
   </si>
   <si>
     <t>Акконд Крекер с солью 255г/12</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_171.png</t>
+    <t>Screenshot_171.png</t>
   </si>
   <si>
     <t>Акконд крекер фас. Крекерсы со вкус. Итальян. сыра 180г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_163.png</t>
+    <t>Screenshot_163.png</t>
   </si>
   <si>
     <t>Акконд паста шок. Добрянка фундук ореховая 340г/12</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/016.png</t>
+    <t>016.png</t>
   </si>
   <si>
     <t>Акконд печ. вес. АККОНДОВСКОЕ Мария 1/3.5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_150.png</t>
+    <t>Screenshot_150.png</t>
   </si>
   <si>
     <t>Акконд печ. вес. АККОНДОВСКОЕ Пухлячок 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_154.png</t>
+    <t>Screenshot_154.png</t>
   </si>
   <si>
     <t>Акконд печ. вес. Вёрсты Аккондовские 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_155.png</t>
+    <t>Screenshot_155.png</t>
   </si>
   <si>
     <t>Акконд печ. вес. Галеты классические 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_174.png</t>
+    <t>Screenshot_174.png</t>
   </si>
   <si>
     <t>Акконд печ. вес. Добрянка фундук печенье-сэндвич 1/3</t>
   </si>
   <si>
-    <t xml:space="preserve">file:///C:/catalog/photos/Screenshot_135.png
-</t>
+    <t>Screenshot_135.png</t>
   </si>
   <si>
     <t>Акконд печ. вес. ТРИО какао с начинкой "пломбир" 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_130.png</t>
+    <t>Screenshot_130.png</t>
   </si>
   <si>
     <t>Акконд печ. фас. ТРИО Джуниор "ванильный бум" 45г/20</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_132.png</t>
+    <t>Screenshot_132.png</t>
   </si>
   <si>
     <t>Акконд печ. фас. ТРИО Джуниор "шоколадный бум" 45г/20</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_133.png</t>
+    <t>Screenshot_133.png</t>
   </si>
   <si>
     <t>Акконд печ. фас. ТРИО Джуниор "шоколадный бум" 45г/80</t>
@@ -483,25 +482,25 @@
     <t>Коробочные конфеты</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/020.png</t>
+    <t>020.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Адель с цельн.миндалем 130г/10 (сладкое спасибо)</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/003.png</t>
+    <t>003.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Адель с цельн.миндалем 150г/6</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/004.png</t>
+    <t>004.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Адель с цельн.миндалем и вишней 150г/6</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/005.png</t>
+    <t>005.png</t>
   </si>
   <si>
     <t>Аленка 150г.1х12 Бисквит сливочный крем</t>
@@ -2865,7 +2864,7 @@
     <t>Акконд  Лав Стори (Love Story) Горький шоколад 82г/22</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_187.png</t>
+    <t>Screenshot_187.png</t>
   </si>
   <si>
     <t>Настоящий горький шоколад с 64% содержанием какао в формате плитки</t>
@@ -2874,7 +2873,7 @@
     <t>Акконд батончик Прохлада с кокосом конфеты 40г/40</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/056.png</t>
+    <t>056.png</t>
   </si>
   <si>
     <t>Конфеты глазированные на основе воздушной нуги с кокосовой стружкой</t>
@@ -2883,7 +2882,7 @@
     <t>Акконд батончик Слимо хрустящие с арахисом конфета 28г/60</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/055.png</t>
+    <t>055.png</t>
   </si>
   <si>
     <t>Батончик оригинальный глазированный на основе хрустящей грильяжной массы с дроблёным арахисом</t>
@@ -2892,7 +2891,7 @@
     <t>Акконд вес. вафли На сорбите 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_128.png</t>
+    <t>Screenshot_128.png</t>
   </si>
   <si>
     <t>Вафли воздушные хрустящие на сорбите</t>
@@ -2901,7 +2900,7 @@
     <t>Акконд вес. конфеты LA LADGE dark cake чизкейк 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/071.png</t>
+    <t>071.png</t>
   </si>
   <si>
     <t>Конфеты глазированные на основе суфле и тёмного слоя с кусочками печенья</t>
@@ -2910,7 +2909,7 @@
     <t>Акконд вес. конфеты LA LADGE milk cake чизкейк 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/072.png</t>
+    <t>072.png</t>
   </si>
   <si>
     <t>Конфеты глазированные на основе суфле и светлого слоя с кусочками печенья</t>
@@ -2919,7 +2918,7 @@
     <t>Акконд вес. конфеты Аккондовская КАРТОШКА 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/099.png</t>
+    <t>099.png</t>
   </si>
   <si>
     <t>Конфеты неглазированные декорированные на основе бисквитной массы с кремовой начинкой на основе какао</t>
@@ -2928,13 +2927,13 @@
     <t>Акконд вес. конфеты Аккондовская КАРТОШКА c СУФЛЕ 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/102.png</t>
+    <t>102.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Аккондовская КАРТОШКА глазированные 1/3 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/100.png</t>
+    <t>100.png</t>
   </si>
   <si>
     <t>Конфеты глазированные декорированные на основе бисквитной массы с кремовой начинкой на основе какао</t>
@@ -2943,7 +2942,7 @@
     <t>Акконд вес. конфеты вафли Аккондовские с халвой 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_38.png</t>
+    <t>Screenshot_38.png</t>
   </si>
   <si>
     <t>Вафли воздушные хрустящие с халвой</t>
@@ -2952,7 +2951,7 @@
     <t>Акконд вес. конфеты ДежаВю со вкусом Вишни с коньяком 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_4.png</t>
+    <t>Screenshot_4.png</t>
   </si>
   <si>
     <t>Конфеты ассорти на основе желейной массы со вкусом вишни с коньяком</t>
@@ -2961,7 +2960,7 @@
     <t>Акконд вес. конфеты ДежаВю со вкусом Сливочного ликёра 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_5.png</t>
+    <t>Screenshot_5.png</t>
   </si>
   <si>
     <t>Конфеты ассорти на основе молочной помады со вкусом сливочного ликёра</t>
@@ -2970,7 +2969,7 @@
     <t>Акконд вес. конфеты Добрянка делямусс фундук десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/044.png</t>
+    <t>044.png</t>
   </si>
   <si>
     <t>Десерт в молочной шоколадной глазури, сочетающий в себе вафельный корпус с аэрированной начинкой на основе фундука в обсыпке крупкой темного печенья</t>
@@ -2979,7 +2978,7 @@
     <t>Акконд вес. конфеты Добрянка делямусс шоколад десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/045.png</t>
+    <t>045.png</t>
   </si>
   <si>
     <t>Десерт в молочной шоколадной глазури, сочетающий в себе вафельный корпус с шоколадной аэрированной начинкой в обсыпке крупкой темного печенья</t>
@@ -2988,7 +2987,7 @@
     <t>Акконд вес. конфеты Добрянка фундук  десерт 4кг УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/042.png</t>
+    <t>042.png</t>
   </si>
   <si>
     <t>Десерт в глазури с кремовой начинкой с добавлением крупки фундука в вафельном корпусе с обсыпкой воздушным рисом</t>
@@ -2997,7 +2996,7 @@
     <t>Акконд вес. конфеты желейные УМИ со вкусом Манго 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_78.png</t>
+    <t>Screenshot_78.png</t>
   </si>
   <si>
     <t>Конфеты неглазированные желейные на основе пектина со вкусом Манго</t>
@@ -3006,7 +3005,7 @@
     <t>Акконд вес. конфеты желейные УМИ со вкусом Юзу 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_76.png</t>
+    <t>Screenshot_76.png</t>
   </si>
   <si>
     <t>Конфеты неглазированные желейные на основе пектина со вкусом Юзу</t>
@@ -3015,7 +3014,7 @@
     <t>Акконд вес. конфеты желейные ФРУ 7 со вкусом Дыни 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_73.png</t>
+    <t>Screenshot_73.png</t>
   </si>
   <si>
     <t>Конфеты неглазированные желейные с начинкой со вкусом дыни</t>
@@ -3024,7 +3023,7 @@
     <t>Акконд вес. конфеты Зачарованные 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_81.png</t>
+    <t>Screenshot_81.png</t>
   </si>
   <si>
     <t>Конфеты глазированные желейно-молочные с начинкой тоффи</t>
@@ -3033,7 +3032,7 @@
     <t>Акконд вес. конфеты Золотая пора "COFFEE" 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_203.png</t>
+    <t>Screenshot_203.png</t>
   </si>
   <si>
     <t>Конфеты глазированные с корпусом тоффи с кремово-молочной начинкой</t>
@@ -3042,19 +3041,19 @@
     <t>Акконд вес. конфеты Золотая пора "TRUFFLE" 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_204.png</t>
+    <t>Screenshot_204.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Золотая пора 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_63.png</t>
+    <t>Screenshot_63.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Золотая пора с кокосом 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_64.png</t>
+    <t>Screenshot_64.png</t>
   </si>
   <si>
     <t>Конфеты глазированные с корпусом тоффи с кремово-молочной начинкой с кокосом</t>
@@ -3063,7 +3062,7 @@
     <t>Акконд вес. конфеты Коффано ТИРАМИСУ 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/073.png</t>
+    <t>073.png</t>
   </si>
   <si>
     <t>Конфеты глазированные с воздушной начинкой итальянского десерта «Тирамису» с уникальным мраморным срезом</t>
@@ -3072,7 +3071,7 @@
     <t>Акконд вес. конфеты Лав Стори (Love Story) с фундуком 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_14.png</t>
+    <t>Screenshot_14.png</t>
   </si>
   <si>
     <t>Конфеты глазированные на основе орехового пралине с вложением цельного ореха фундука</t>
@@ -3081,7 +3080,7 @@
     <t>Акконд вес. конфеты Ласка с арахисом 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_9.png</t>
+    <t>Screenshot_9.png</t>
   </si>
   <si>
     <t>Конфеты ассорти с арахисовой начинкой, глазированные</t>
@@ -3090,7 +3089,7 @@
     <t>Акконд вес. конфеты Ласка с коньяком 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_11.png</t>
+    <t>Screenshot_11.png</t>
   </si>
   <si>
     <t>Конфеты ассорти с коньячной начинкой, глазированные</t>
@@ -3099,7 +3098,7 @@
     <t>Акконд вес. конфеты Ласка с фундуком 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_8.png</t>
+    <t>Screenshot_8.png</t>
   </si>
   <si>
     <t>Конфеты ассорти с двухслойной кремовой начинкой и цельным фундуком, глазированные</t>
@@ -3108,7 +3107,7 @@
     <t>Акконд вес. конфеты Леди День кокос 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/082.png</t>
+    <t>082.png</t>
   </si>
   <si>
     <t>Конфеты оригинальные на основе суфле и кокосовой стружки, покрытые белой глазурью и декорированные</t>
@@ -3117,7 +3116,7 @@
     <t>Акконд вес. конфеты Леди Ночь кокос 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/077.png</t>
+    <t>077.png</t>
   </si>
   <si>
     <t>Конфеты оригинальные на основе суфле и кокосовой стружки, глазированные и декорированные</t>
@@ -3126,7 +3125,7 @@
     <t>Акконд вес. конфеты Ломтишка 2кг уп</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_205.png</t>
+    <t>Screenshot_205.png</t>
   </si>
   <si>
     <t>Десерт, сочетающий нежные бисквитные ломтики с кремовой начинкой, декорированный глазурью</t>
@@ -3135,7 +3134,7 @@
     <t>Акконд вес. конфеты Ломтишка глазированный десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/028.png</t>
+    <t>028.png</t>
   </si>
   <si>
     <t>Десерт, сочетающий нежные бисквитные ломтики с кремовой начинкой, глазированный и декорированный глазурью</t>
@@ -3144,7 +3143,7 @@
     <t>Акконд вес. конфеты Ломтишка молоко десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/027.png</t>
+    <t>027.png</t>
   </si>
   <si>
     <t>Десерт, сочетающий нежные бисквитные ломтики с кремовой молочной начинкой, декорированный глазурью</t>
@@ -3153,7 +3152,7 @@
     <t>Акконд вес. конфеты Малена со вкусом Апельсина и Сливок 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/106.png</t>
+    <t>106.png</t>
   </si>
   <si>
     <t>Оригинальный зефир со вкусом апельсина и сливок в шоколаде</t>
@@ -3162,7 +3161,7 @@
     <t>Акконд вес. конфеты Малена со вкусом Клубники и Сливок 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/107.png</t>
+    <t>107.png</t>
   </si>
   <si>
     <t>Оригинальный зефир со вкусом клубники и сливок в шоколаде</t>
@@ -3171,7 +3170,7 @@
     <t>Акконд вес. конфеты МНЕ БЕЗ САХАРА молочные вафли 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_126.png</t>
+    <t>Screenshot_126.png</t>
   </si>
   <si>
     <t>Вафли воздушные хрустящие с нежным молочным вкусом на основе натуральных сахарозаменителей</t>
@@ -3180,7 +3179,7 @@
     <t>Акконд вес. конфеты МНЕ БЕЗ САХАРА молочный мини-шоколад 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/024.png</t>
+    <t>024.png</t>
   </si>
   <si>
     <t>Настоящий 100% молочный шоколад оригинальной дизайнерской формы</t>
@@ -3189,7 +3188,7 @@
     <t>Акконд вес. конфеты МНЕ БЕЗ САХАРА с какао вафли 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_127.png</t>
+    <t>Screenshot_127.png</t>
   </si>
   <si>
     <t>Вафли воздушные хрустящие с какао на основе натуральных сахарозаменителей</t>
@@ -3198,7 +3197,7 @@
     <t>Акконд вес. конфеты МНЕ БЕЗ САХАРА тёмный мини-шоколад 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/023.png</t>
+    <t>023.png</t>
   </si>
   <si>
     <t>Тёмный мини-шоколад на основе натуральных сахорозаменителей</t>
@@ -3207,7 +3206,7 @@
     <t>Акконд вес. конфеты Молочная речка Апельсиновые берега 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_69.png</t>
+    <t>Screenshot_69.png</t>
   </si>
   <si>
     <t>Конфеты неглазированные на основе молочно-ирисной массы с нежной молочно-кремовой начинкой</t>
@@ -3216,25 +3215,25 @@
     <t>Акконд вес. конфеты Молочная речка Арбузные берега 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_68.png</t>
+    <t>Screenshot_68.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Молочная речка Вишнёвые берега 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_67.png</t>
+    <t>Screenshot_67.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Молочная речка Клубничные берега 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_66.png</t>
+    <t>Screenshot_66.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Муррлинка со вкусом клубники и сливок 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_61.png</t>
+    <t>Screenshot_61.png</t>
   </si>
   <si>
     <t>Конфеты глазированные с двухслойной желейной начинкой со вкусом клубники и сливок</t>
@@ -3243,7 +3242,7 @@
     <t>Акконд вес. конфеты Орешка с цельным фундуком со вкусом Сливок 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/091.png</t>
+    <t>091.png</t>
   </si>
   <si>
     <t>Конфеты глазированные молочной шоколадной глазурью, сочетающие в себе вафельный корпус и нежную кремовую начинку со вкусом сливок, с вложением цельного фундука</t>
@@ -3252,7 +3251,7 @@
     <t>Акконд вес. конфеты Орешка с цельным фундуком со вкусом Шоколада 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/092.png</t>
+    <t>092.png</t>
   </si>
   <si>
     <t>Конфеты глазированные молочной шоколадной глазурью, сочетающие в себе вафельный корпус и нежную кремовую начинку со вкусом шоколада, с вложением цельного фундука</t>
@@ -3261,7 +3260,7 @@
     <t>Акконд вес. конфеты От Красули 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_80.png</t>
+    <t>Screenshot_80.png</t>
   </si>
   <si>
     <t>Конфеты неглазированные молочные с тянущейся начинкой</t>
@@ -3270,7 +3269,7 @@
     <t>Акконд вес. конфеты Отломи 1/4кг</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/083.png</t>
+    <t>083.png</t>
   </si>
   <si>
     <t>Батончик оригинальный вафельный с молочной карамелью и кремовой начинкой, посыпанный крупкой арахиса и воздушным рисом, глазированный</t>
@@ -3279,7 +3278,7 @@
     <t>Акконд вес. конфеты Отломи Pralineo 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_25.png</t>
+    <t>Screenshot_25.png</t>
   </si>
   <si>
     <t>Конфеты на основе нежного пралине со вкусом конфет «Отломи» в карамели и обсыпке арахисом, глазированные</t>
@@ -3288,7 +3287,7 @@
     <t>Акконд вес. конфеты Отломи неглазированные 1/4кг</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/086.png</t>
+    <t>086.png</t>
   </si>
   <si>
     <t>Конфеты оригинальные вафельные с молочной карамелью и кремовой начинкой, обсыпанные крупкой арахиса и воздушным рисом, частично глазированные</t>
@@ -3297,7 +3296,7 @@
     <t>Акконд вес. конфеты Отломи с арахисовой начинкой 1/4кг</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/085.png</t>
+    <t>085.png</t>
   </si>
   <si>
     <t>Глазированные вафельные конфеты с молочной карамелью и арахисовой начинкой, посыпанные крупкой арахиса и воздушным рисом</t>
@@ -3306,7 +3305,7 @@
     <t>Акконд вес. конфеты Просто вишня 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_1.png</t>
+    <t>Screenshot_1.png</t>
   </si>
   <si>
     <t>Конфеты премиум класса с цельной вишней в ликёре</t>
@@ -3315,13 +3314,13 @@
     <t>Акконд вес. конфеты Просто вишня Cherry Drop 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_206.png</t>
+    <t>Screenshot_206.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Прохлада с кокосом конфеты 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_43.png</t>
+    <t>Screenshot_43.png</t>
   </si>
   <si>
     <t>Акконд вес. конфеты Прохлада с кокосом конфеты 1/4 Мега</t>
@@ -3330,7 +3329,7 @@
     <t>Акконд вес. конфеты Птица дивная в шоколадной глазури 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/066.png</t>
+    <t>066.png</t>
   </si>
   <si>
     <t>Конфеты глазированные на основе сливочного суфле, изготовленного на 100% сливочном масле</t>
@@ -3351,7 +3350,7 @@
     <t>Акконд вес. конфеты Рулада арахис десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/047.png</t>
+    <t>047.png</t>
   </si>
   <si>
     <t>Десерт глазированный в вафельном корпусе в обсыпке крупкой арахиса с кремовой начинкой на основе арахиса</t>
@@ -3360,7 +3359,7 @@
     <t>Акконд вес. конфеты Рулада сливки десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/048.png</t>
+    <t>048.png</t>
   </si>
   <si>
     <t>Десерт глазированный в вафельном корпусе в обсыпке крупкой арахиса с кремовой начинкой на основа сливок</t>
@@ -3369,7 +3368,7 @@
     <t>Акконд вес. конфеты Рулада фундук десерт 1/2 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/046.png</t>
+    <t>046.png</t>
   </si>
   <si>
     <t>Десерт глазированный в вафельном корпусе в обсыпке крупкой арахиса с кремовой начинкой на основе фундука</t>
@@ -3378,7 +3377,7 @@
     <t>Акконд вес. конфеты Слимо кофейные хрустящие 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_90.png</t>
+    <t>Screenshot_90.png</t>
   </si>
   <si>
     <t>Конфеты хрустящие глазированные из хрустящей грильяжной массы с кофейной ноткой</t>
@@ -3387,7 +3386,7 @@
     <t>Акконд вес. конфеты Трамвайчик нуга с арахисом 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_50.png</t>
+    <t>Screenshot_50.png</t>
   </si>
   <si>
     <t>Конфеты мягкие неглазированные из аэрированной нуги с арахисом</t>
@@ -3396,7 +3395,7 @@
     <t>Акконд вес. конфеты Трюфель 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_16.png</t>
+    <t>Screenshot_16.png</t>
   </si>
   <si>
     <t>Роскошный классический трюфель в лёгкой обсыпке из натурального какао-порошка</t>
@@ -3405,7 +3404,7 @@
     <t>Акконд вес. конфеты Фараделла глазированный десерт 1/3 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/040.png</t>
+    <t>040.png</t>
   </si>
   <si>
     <t>Десерт, сочетающий в себе вафельный корпус, кремовую начинку и обсыпку крупкой темного печенья, глазированный</t>
@@ -3414,7 +3413,7 @@
     <t>Акконд вес. конфеты Фараделла десерт 1/3 УПК</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/038.png</t>
+    <t>038.png</t>
   </si>
   <si>
     <t>Десерт с глазированным донышком, сочетающий в себе вафельный корпус со сливочной кремовой начинкой в карамели с обсыпкой крупкой арахиса</t>
@@ -3423,7 +3422,7 @@
     <t>Акконд вес. конфеты Фараделла с печеньем ТРИО десерт 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/041.png</t>
+    <t>041.png</t>
   </si>
   <si>
     <t>Десерт с глазированным донышком, сочетающий в себе вафельный корпус, кремовую начинку и обсыпку крупкой печенья «ТРИО»</t>
@@ -3438,7 +3437,7 @@
     <t>Акконд вес. конфеты Хрустальное озеро 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_29.png</t>
+    <t>Screenshot_29.png</t>
   </si>
   <si>
     <t>Конфеты удлинённой формы глазированные на основе молочного пралине с добавлением крошки крекера и тёртого арахиса</t>
@@ -3447,7 +3446,7 @@
     <t>Акконд вес. конфеты Шоко Бар с печеньем и арахисом  1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_207.png</t>
+    <t>Screenshot_207.png</t>
   </si>
   <si>
     <t>Конфеты оригинальные удлинённые на основе затяжного печенья, покрытого молочной карамелью, обсыпанные крупкой арахиса и воздушным рисом, частично глазированные</t>
@@ -3456,7 +3455,7 @@
     <t>Акконд вес. конфеты Ярмила с бисквитом 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_208.png</t>
+    <t>Screenshot_208.png</t>
   </si>
   <si>
     <t>Конфеты глазированные из молочной массы с добавлением кусочков бисквита</t>
@@ -3465,7 +3464,7 @@
     <t>Акконд крекер вес. АККОНДОВСКИЙ с солью со вкусом сметаны и лука 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_177.png</t>
+    <t>Screenshot_177.png</t>
   </si>
   <si>
     <t>Крекер из пшеничной муки высшего сорта с посыпкой солью, со вкусом сметаны и лука</t>
@@ -3474,7 +3473,7 @@
     <t>Акконд крекер вес. Калейдоскоп улыбок 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_168.png</t>
+    <t>Screenshot_168.png</t>
   </si>
   <si>
     <t>Крекер с разными формами</t>
@@ -3483,7 +3482,7 @@
     <t>Акконд крекер вес. Русалочкин хоровод 1/5</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_167.png</t>
+    <t>Screenshot_167.png</t>
   </si>
   <si>
     <t>Крекер в форме рыбок из муки высшего сорта с разными вкусами: с розмарином, семенами льна, луком</t>
@@ -3492,8 +3491,7 @@
     <t>Акконд крекер вес. с солью мини 1/4</t>
   </si>
   <si>
-    <t xml:space="preserve">file:///C:/catalog/photos/Screenshot_173.png
-</t>
+    <t>Screenshot_173.png</t>
   </si>
   <si>
     <t>Крекер из пшеничной муки высшего сорта с посыпкой солью с разными вкусами: лука и укропа, сметаны и лука</t>
@@ -3502,7 +3500,7 @@
     <t>Акконд крекер фас. Крекерсы картофельный оригинальный 150г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_162.png</t>
+    <t>Screenshot_162.png</t>
   </si>
   <si>
     <t>Лёгкий и хрустящий крекер из картофеля без обжарки</t>
@@ -3511,7 +3509,7 @@
     <t>Акконд крекер фас. Крекерсы с солью 180г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_165.png</t>
+    <t>Screenshot_165.png</t>
   </si>
   <si>
     <t>Лёгкий и хрустящий солёный крекер</t>
@@ -3520,7 +3518,7 @@
     <t>Акконд крекер фас. Крекерсы со вкус.сметаны и зелени 180г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_164.png</t>
+    <t>Screenshot_164.png</t>
   </si>
   <si>
     <t>Лёгкий и хрустящий солёный крекер с ароматом сметаны и зеленью</t>
@@ -3529,7 +3527,7 @@
     <t>Акконд крекер фас. Мистер рыбка 300г/11</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_166.png</t>
+    <t>Screenshot_166.png</t>
   </si>
   <si>
     <t>Цветной крекер в форме рыбок из муки высшего сорта</t>
@@ -3541,7 +3539,7 @@
     <t>Акконд крекер фас. Полька со вкусом ЛУКА и УКРОПА 300г/10</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_169.png</t>
+    <t>Screenshot_169.png</t>
   </si>
   <si>
     <t>Хрустящий солёный крекер с ароматной зеленью и луком</t>
@@ -3550,7 +3548,7 @@
     <t>Акконд крекер фас. Полька со вкусом СМЕТАНЫ и ЛУКА 300г/10</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_170.png</t>
+    <t>Screenshot_170.png</t>
   </si>
   <si>
     <t>Хрустящий солёный крекер с ароматом сметаны и лука</t>
@@ -3562,7 +3560,7 @@
     <t>Акконд паста шок. Отломи шоколадно-ореховая паста 330г/12</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/015.png</t>
+    <t>015.png</t>
   </si>
   <si>
     <t>Кремовая паста на основе натурального арахиса, ореха фундука и шоколада</t>
@@ -3577,7 +3575,7 @@
     <t>Акконд печ. вес. Карамелизированное 1/4</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_139.png</t>
+    <t>Screenshot_139.png</t>
   </si>
   <si>
     <t>Печенье сахарное с нотками корицы из пшеничной и овсяной муки высшего сорта</t>
@@ -3586,7 +3584,7 @@
     <t>Акконд печ. вес. ТРИО какао с начинкой "шоколадный брауни" 1/3</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_131.png</t>
+    <t>Screenshot_131.png</t>
   </si>
   <si>
     <t>Оригинальное трёхслойное печенье, сочетающее тёмное хрустящее печенье и кремовую начинку с шоколадным вкусом, 45 г</t>
@@ -3595,7 +3593,7 @@
     <t>Акконд печ. фас. Аккондовское со сливочным вкусом 285г/12</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_138.png</t>
+    <t>Screenshot_138.png</t>
   </si>
   <si>
     <t>Печенье сахарное из пшеничной муки высшего сорта со сливочным вкусом</t>
@@ -3604,7 +3602,7 @@
     <t>Акконд печ. фас. Мария 200г/16</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_209.png</t>
+    <t>Screenshot_209.png</t>
   </si>
   <si>
     <t>Печенье затяжное с молочным вкусом из пшеничной муки высшего сорта</t>
@@ -3622,7 +3620,7 @@
     <t>Акконд торт глазированный Ломтишка 380г/9</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/019.png</t>
+    <t>019.png</t>
   </si>
   <si>
     <t>Глазированный торт с нежным бисквитом и кремовой начинкой</t>
@@ -3631,19 +3629,19 @@
     <t>Акконд фас. конфеты Отломи 200г/10</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_211.png</t>
+    <t>Screenshot_211.png</t>
   </si>
   <si>
     <t>Акконд фас. конфеты Отломи 360г/7</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_210.png</t>
+    <t>Screenshot_210.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Болетто конфеты 225г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/001.png</t>
+    <t>001.png</t>
   </si>
   <si>
     <t>Конфеты эксклюзивные в форме грибочков на основе сливочного суфле, изготовленного на 100% сливочном масле, глазированные шоколадом</t>
@@ -3652,7 +3650,7 @@
     <t>Акконд фас. кор. конфеты Лав Стори (Love Story) 250г/10</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/013.png</t>
+    <t>013.png</t>
   </si>
   <si>
     <t>Конфеты глазированные на основе миндального пралине с вложением цельного ореха миндаля</t>
@@ -3661,13 +3659,13 @@
     <t>Акконд фас. кор. конфеты Орешка с цельным фундуком со вкусом Сливок 100г/18 цветы</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_212.png</t>
+    <t>Screenshot_212.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Поздравляю 180г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/008.png</t>
+    <t>008.png</t>
   </si>
   <si>
     <t>Конфеты глазированные с цельным фундуком на основе фундучной начинки</t>
@@ -3676,19 +3674,19 @@
     <t>Акконд фас. кор. конфеты Просто вишня 190г/8</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/009.png</t>
+    <t>009.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Птица дивная в шок глазури 300г/15</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/002.png</t>
+    <t>002.png</t>
   </si>
   <si>
     <t>Акконд фас. кор. конфеты Хрум-Хрум с кунжутом 200г/16</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_92.png</t>
+    <t>Screenshot_92.png</t>
   </si>
   <si>
     <t>Конфеты из хрустящей грильяжной массы с добавлением кунжута</t>
@@ -3697,7 +3695,7 @@
     <t>Акконд шоколад молочный 90г/20 (2)</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_185.png</t>
+    <t>Screenshot_185.png</t>
   </si>
   <si>
     <t>Настоящий молочный шоколад с содержанием цельного молока в формате плитки</t>
@@ -3706,7 +3704,7 @@
     <t>Акконд шоколад Шоко-кроко молочный со злаками 23г/24</t>
   </si>
   <si>
-    <t>file:///C:/catalog/photos/Screenshot_186.png</t>
+    <t>Screenshot_186.png</t>
   </si>
   <si>
     <t>Десерт "Ломтишка" 160 гр. (9) АККОНД</t>
@@ -3728,7 +3726,7 @@
     <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3764,13 +3762,6 @@
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4266,148 +4257,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6094,7 +6085,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="71" ht="43.2" spans="1:5">
+    <row r="71" ht="43.2" customHeight="1" spans="1:5">
       <c r="A71" s="7" t="s">
         <v>139</v>
       </c>
@@ -20224,7 +20215,7 @@
         <v>❌</v>
       </c>
     </row>
-    <row r="856" ht="27.6" spans="1:5">
+    <row r="856" ht="27.6" customHeight="1" spans="1:5">
       <c r="A856" s="14" t="s">
         <v>943</v>
       </c>
@@ -20242,7 +20233,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="857" ht="27.6" spans="1:5">
+    <row r="857" ht="27.6" customHeight="1" spans="1:5">
       <c r="A857" s="17" t="s">
         <v>946</v>
       </c>
@@ -20260,7 +20251,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="858" ht="27.6" spans="1:5">
+    <row r="858" ht="27.6" customHeight="1" spans="1:5">
       <c r="A858" s="14" t="s">
         <v>949</v>
       </c>
@@ -20296,7 +20287,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="860" ht="27.6" spans="1:5">
+    <row r="860" ht="27.6" customHeight="1" spans="1:5">
       <c r="A860" s="14" t="s">
         <v>955</v>
       </c>
@@ -20314,7 +20305,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="861" ht="27.6" spans="1:5">
+    <row r="861" ht="27.6" customHeight="1" spans="1:5">
       <c r="A861" s="17" t="s">
         <v>958</v>
       </c>
@@ -20332,7 +20323,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="862" ht="27.6" spans="1:5">
+    <row r="862" ht="27.6" customHeight="1" spans="1:5">
       <c r="A862" s="14" t="s">
         <v>961</v>
       </c>
@@ -20350,7 +20341,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="863" ht="27.6" spans="1:5">
+    <row r="863" ht="27.6" customHeight="1" spans="1:5">
       <c r="A863" s="17" t="s">
         <v>964</v>
       </c>
@@ -20368,7 +20359,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="864" ht="27.6" spans="1:5">
+    <row r="864" ht="27.6" customHeight="1" spans="1:5">
       <c r="A864" s="14" t="s">
         <v>966</v>
       </c>
@@ -20404,7 +20395,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="866" ht="27.6" spans="1:5">
+    <row r="866" ht="27.6" customHeight="1" spans="1:5">
       <c r="A866" s="14" t="s">
         <v>972</v>
       </c>
@@ -20422,7 +20413,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="867" ht="27.6" spans="1:5">
+    <row r="867" ht="27.6" customHeight="1" spans="1:5">
       <c r="A867" s="17" t="s">
         <v>975</v>
       </c>
@@ -20440,7 +20431,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="868" ht="41.4" spans="1:5">
+    <row r="868" ht="41.4" customHeight="1" spans="1:5">
       <c r="A868" s="14" t="s">
         <v>978</v>
       </c>
@@ -20458,7 +20449,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="869" ht="41.4" spans="1:5">
+    <row r="869" ht="41.4" customHeight="1" spans="1:5">
       <c r="A869" s="17" t="s">
         <v>981</v>
       </c>
@@ -20476,7 +20467,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="870" ht="27.6" spans="1:5">
+    <row r="870" ht="27.6" customHeight="1" spans="1:5">
       <c r="A870" s="14" t="s">
         <v>984</v>
       </c>
@@ -20494,7 +20485,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="871" ht="27.6" spans="1:5">
+    <row r="871" ht="27.6" customHeight="1" spans="1:5">
       <c r="A871" s="17" t="s">
         <v>987</v>
       </c>
@@ -20566,7 +20557,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="875" ht="27.6" spans="1:5">
+    <row r="875" ht="27.6" customHeight="1" spans="1:5">
       <c r="A875" s="17" t="s">
         <v>999</v>
       </c>
@@ -20584,7 +20575,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="876" ht="27.6" spans="1:5">
+    <row r="876" ht="27.6" customHeight="1" spans="1:5">
       <c r="A876" s="14" t="s">
         <v>1002</v>
       </c>
@@ -20602,7 +20593,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="877" ht="27.6" spans="1:5">
+    <row r="877" ht="27.6" customHeight="1" spans="1:5">
       <c r="A877" s="17" t="s">
         <v>1004</v>
       </c>
@@ -20620,7 +20611,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="878" ht="27.6" spans="1:5">
+    <row r="878" ht="27.6" customHeight="1" spans="1:5">
       <c r="A878" s="14" t="s">
         <v>1006</v>
       </c>
@@ -20638,7 +20629,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="879" ht="27.6" spans="1:5">
+    <row r="879" ht="27.6" customHeight="1" spans="1:5">
       <c r="A879" s="17" t="s">
         <v>1009</v>
       </c>
@@ -20656,7 +20647,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="880" ht="27.6" spans="1:5">
+    <row r="880" ht="27.6" customHeight="1" spans="1:5">
       <c r="A880" s="14" t="s">
         <v>1012</v>
       </c>
@@ -20710,7 +20701,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="883" ht="27.6" spans="1:5">
+    <row r="883" ht="27.6" customHeight="1" spans="1:5">
       <c r="A883" s="17" t="s">
         <v>1021</v>
       </c>
@@ -20728,7 +20719,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="884" ht="27.6" spans="1:5">
+    <row r="884" ht="27.6" customHeight="1" spans="1:5">
       <c r="A884" s="14" t="s">
         <v>1024</v>
       </c>
@@ -20746,7 +20737,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="885" ht="27.6" spans="1:5">
+    <row r="885" ht="27.6" customHeight="1" spans="1:5">
       <c r="A885" s="17" t="s">
         <v>1027</v>
       </c>
@@ -20764,7 +20755,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="886" ht="27.6" spans="1:5">
+    <row r="886" ht="27.6" customHeight="1" spans="1:5">
       <c r="A886" s="14" t="s">
         <v>1030</v>
       </c>
@@ -20782,7 +20773,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="887" ht="27.6" spans="1:5">
+    <row r="887" ht="27.6" customHeight="1" spans="1:5">
       <c r="A887" s="17" t="s">
         <v>1033</v>
       </c>
@@ -20800,7 +20791,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="888" ht="27.6" spans="1:5">
+    <row r="888" ht="27.6" customHeight="1" spans="1:5">
       <c r="A888" s="14" t="s">
         <v>1036</v>
       </c>
@@ -20854,7 +20845,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="891" ht="27.6" spans="1:5">
+    <row r="891" ht="27.6" customHeight="1" spans="1:5">
       <c r="A891" s="17" t="s">
         <v>1045</v>
       </c>
@@ -20872,7 +20863,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="892" ht="27.6" spans="1:5">
+    <row r="892" ht="27.6" customHeight="1" spans="1:5">
       <c r="A892" s="14" t="s">
         <v>1048</v>
       </c>
@@ -20890,7 +20881,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="893" ht="27.6" spans="1:5">
+    <row r="893" ht="27.6" customHeight="1" spans="1:5">
       <c r="A893" s="17" t="s">
         <v>1051</v>
       </c>
@@ -20926,7 +20917,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="895" ht="27.6" spans="1:5">
+    <row r="895" ht="27.6" customHeight="1" spans="1:5">
       <c r="A895" s="17" t="s">
         <v>1057</v>
       </c>
@@ -20944,7 +20935,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="896" ht="27.6" spans="1:5">
+    <row r="896" ht="27.6" customHeight="1" spans="1:5">
       <c r="A896" s="14" t="s">
         <v>1060</v>
       </c>
@@ -20962,7 +20953,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="897" ht="27.6" spans="1:5">
+    <row r="897" ht="27.6" customHeight="1" spans="1:5">
       <c r="A897" s="17" t="s">
         <v>1062</v>
       </c>
@@ -20980,7 +20971,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="898" ht="27.6" spans="1:5">
+    <row r="898" ht="27.6" customHeight="1" spans="1:5">
       <c r="A898" s="14" t="s">
         <v>1064</v>
       </c>
@@ -20998,7 +20989,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="899" ht="27.6" spans="1:5">
+    <row r="899" ht="27.6" customHeight="1" spans="1:5">
       <c r="A899" s="17" t="s">
         <v>1066</v>
       </c>
@@ -21016,7 +21007,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="900" ht="41.4" spans="1:5">
+    <row r="900" ht="41.4" customHeight="1" spans="1:5">
       <c r="A900" s="14" t="s">
         <v>1069</v>
       </c>
@@ -21034,7 +21025,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="901" ht="41.4" spans="1:5">
+    <row r="901" ht="41.4" customHeight="1" spans="1:5">
       <c r="A901" s="17" t="s">
         <v>1072</v>
       </c>
@@ -21070,7 +21061,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="903" ht="41.4" spans="1:5">
+    <row r="903" ht="41.4" customHeight="1" spans="1:5">
       <c r="A903" s="17" t="s">
         <v>1078</v>
       </c>
@@ -21088,7 +21079,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="904" ht="27.6" spans="1:5">
+    <row r="904" ht="27.6" customHeight="1" spans="1:5">
       <c r="A904" s="14" t="s">
         <v>1081</v>
       </c>
@@ -21106,7 +21097,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="905" ht="41.4" spans="1:5">
+    <row r="905" ht="41.4" customHeight="1" spans="1:5">
       <c r="A905" s="17" t="s">
         <v>1084</v>
       </c>
@@ -21124,7 +21115,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="906" ht="27.6" spans="1:5">
+    <row r="906" ht="27.6" customHeight="1" spans="1:5">
       <c r="A906" s="14" t="s">
         <v>1087</v>
       </c>
@@ -21178,7 +21169,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="909" ht="27.6" spans="1:5">
+    <row r="909" ht="27.6" customHeight="1" spans="1:5">
       <c r="A909" s="17" t="s">
         <v>1095</v>
       </c>
@@ -21196,7 +21187,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="910" ht="27.6" spans="1:5">
+    <row r="910" ht="27.6" customHeight="1" spans="1:5">
       <c r="A910" s="14" t="s">
         <v>1097</v>
       </c>
@@ -21214,7 +21205,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="911" ht="27.6" spans="1:5">
+    <row r="911" ht="27.6" customHeight="1" spans="1:5">
       <c r="A911" s="17" t="s">
         <v>1098</v>
       </c>
@@ -21232,7 +21223,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="912" ht="27.6" spans="1:5">
+    <row r="912" ht="27.6" customHeight="1" spans="1:5">
       <c r="A912" s="14" t="s">
         <v>1101</v>
       </c>
@@ -21250,7 +21241,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="913" ht="27.6" spans="1:5">
+    <row r="913" ht="27.6" customHeight="1" spans="1:5">
       <c r="A913" s="17" t="s">
         <v>1103</v>
       </c>
@@ -21268,7 +21259,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="914" ht="27.6" spans="1:5">
+    <row r="914" ht="27.6" customHeight="1" spans="1:5">
       <c r="A914" s="14" t="s">
         <v>1105</v>
       </c>
@@ -21286,7 +21277,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="915" ht="27.6" spans="1:5">
+    <row r="915" ht="27.6" customHeight="1" spans="1:5">
       <c r="A915" s="17" t="s">
         <v>1108</v>
       </c>
@@ -21304,7 +21295,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="916" ht="27.6" spans="1:5">
+    <row r="916" ht="27.6" customHeight="1" spans="1:5">
       <c r="A916" s="14" t="s">
         <v>1111</v>
       </c>
@@ -21322,7 +21313,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="917" ht="27.6" spans="1:5">
+    <row r="917" ht="27.6" customHeight="1" spans="1:5">
       <c r="A917" s="17" t="s">
         <v>1114</v>
       </c>
@@ -21358,7 +21349,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="919" ht="27.6" spans="1:5">
+    <row r="919" ht="27.6" customHeight="1" spans="1:5">
       <c r="A919" s="17" t="s">
         <v>1120</v>
       </c>
@@ -21376,7 +21367,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="920" ht="27.6" spans="1:5">
+    <row r="920" ht="27.6" customHeight="1" spans="1:5">
       <c r="A920" s="14" t="s">
         <v>1123</v>
       </c>
@@ -21394,7 +21385,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="921" ht="41.4" spans="1:5">
+    <row r="921" ht="41.4" customHeight="1" spans="1:5">
       <c r="A921" s="17" t="s">
         <v>1126</v>
       </c>
@@ -21412,7 +21403,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="922" ht="27.6" spans="1:5">
+    <row r="922" ht="27.6" customHeight="1" spans="1:5">
       <c r="A922" s="14" t="s">
         <v>1129</v>
       </c>
@@ -21430,7 +21421,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="923" ht="27.6" spans="1:5">
+    <row r="923" ht="27.6" customHeight="1" spans="1:5">
       <c r="A923" s="17" t="s">
         <v>1132</v>
       </c>
@@ -21448,7 +21439,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="924" ht="27.6" spans="1:5">
+    <row r="924" ht="27.6" customHeight="1" spans="1:5">
       <c r="A924" s="14" t="s">
         <v>1134</v>
       </c>
@@ -21466,7 +21457,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="925" ht="41.4" spans="1:5">
+    <row r="925" ht="41.4" customHeight="1" spans="1:5">
       <c r="A925" s="17" t="s">
         <v>1137</v>
       </c>
@@ -21484,7 +21475,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="926" ht="27.6" spans="1:5">
+    <row r="926" ht="27.6" customHeight="1" spans="1:5">
       <c r="A926" s="14" t="s">
         <v>1140</v>
       </c>
@@ -21502,7 +21493,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="927" ht="27.6" spans="1:5">
+    <row r="927" ht="27.6" customHeight="1" spans="1:5">
       <c r="A927" s="17" t="s">
         <v>1143</v>
       </c>
@@ -21538,7 +21529,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="929" ht="27.6" spans="1:5">
+    <row r="929" ht="27.6" customHeight="1" spans="1:5">
       <c r="A929" s="17" t="s">
         <v>1149</v>
       </c>
@@ -21556,7 +21547,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="930" ht="43.2" spans="1:5">
+    <row r="930" ht="43.2" customHeight="1" spans="1:5">
       <c r="A930" s="14" t="s">
         <v>1152</v>
       </c>
@@ -21628,7 +21619,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="934" ht="28.8" spans="1:5">
+    <row r="934" ht="28.8" customHeight="1" spans="1:5">
       <c r="A934" s="14" t="s">
         <v>1164</v>
       </c>
@@ -21700,7 +21691,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="938" ht="27.6" spans="1:5">
+    <row r="938" ht="27.6" customHeight="1" spans="1:5">
       <c r="A938" s="14" t="s">
         <v>1174</v>
       </c>
@@ -21718,7 +21709,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="939" ht="27.6" spans="1:5">
+    <row r="939" ht="27.6" customHeight="1" spans="1:5">
       <c r="A939" s="17" t="s">
         <v>1175</v>
       </c>
@@ -21754,7 +21745,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="941" ht="27.6" spans="1:5">
+    <row r="941" ht="27.6" customHeight="1" spans="1:5">
       <c r="A941" s="17" t="s">
         <v>1180</v>
       </c>
@@ -21772,7 +21763,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="942" ht="27.6" spans="1:5">
+    <row r="942" ht="27.6" customHeight="1" spans="1:5">
       <c r="A942" s="14" t="s">
         <v>1183</v>
       </c>
@@ -21790,7 +21781,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="943" ht="27.6" spans="1:5">
+    <row r="943" ht="27.6" customHeight="1" spans="1:5">
       <c r="A943" s="17" t="s">
         <v>1186</v>
       </c>
@@ -21808,7 +21799,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="944" ht="27.6" spans="1:5">
+    <row r="944" ht="27.6" customHeight="1" spans="1:5">
       <c r="A944" s="14" t="s">
         <v>1189</v>
       </c>
@@ -21826,7 +21817,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="945" ht="27.6" spans="1:5">
+    <row r="945" ht="27.6" customHeight="1" spans="1:5">
       <c r="A945" s="17" t="s">
         <v>1192</v>
       </c>
@@ -21844,7 +21835,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="946" ht="27.6" spans="1:5">
+    <row r="946" ht="27.6" customHeight="1" spans="1:5">
       <c r="A946" s="14" t="s">
         <v>1193</v>
       </c>
@@ -21880,7 +21871,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="948" ht="41.4" spans="1:5">
+    <row r="948" ht="41.4" customHeight="1" spans="1:5">
       <c r="A948" s="14" t="s">
         <v>1198</v>
       </c>
@@ -21898,7 +21889,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="949" ht="41.4" spans="1:5">
+    <row r="949" ht="41.4" customHeight="1" spans="1:5">
       <c r="A949" s="17" t="s">
         <v>1200</v>
       </c>
@@ -21916,7 +21907,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="950" ht="27.6" spans="1:5">
+    <row r="950" ht="27.6" customHeight="1" spans="1:5">
       <c r="A950" s="14" t="s">
         <v>1202</v>
       </c>
@@ -21934,7 +21925,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="951" ht="27.6" spans="1:5">
+    <row r="951" ht="27.6" customHeight="1" spans="1:5">
       <c r="A951" s="17" t="s">
         <v>1205</v>
       </c>
@@ -21952,7 +21943,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="952" ht="41.4" spans="1:5">
+    <row r="952" ht="41.4" customHeight="1" spans="1:5">
       <c r="A952" s="14" t="s">
         <v>1208</v>
       </c>
@@ -21970,7 +21961,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="953" ht="27.6" spans="1:5">
+    <row r="953" ht="27.6" customHeight="1" spans="1:5">
       <c r="A953" s="17" t="s">
         <v>1210</v>
       </c>
@@ -22006,7 +21997,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="955" ht="27.6" spans="1:5">
+    <row r="955" ht="27.6" customHeight="1" spans="1:5">
       <c r="A955" s="17" t="s">
         <v>1215</v>
       </c>
@@ -22042,7 +22033,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="957" ht="27.6" spans="1:5">
+    <row r="957" ht="27.6" customHeight="1" spans="1:5">
       <c r="A957" s="17" t="s">
         <v>1220</v>
       </c>
@@ -22060,7 +22051,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="958" ht="27.6" spans="1:5">
+    <row r="958" ht="27.6" customHeight="1" spans="1:5">
       <c r="A958" s="14" t="s">
         <v>1223</v>
       </c>
@@ -22078,7 +22069,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="959" ht="27.6" spans="1:5">
+    <row r="959" ht="27.6" customHeight="1" spans="1:5">
       <c r="A959" s="17" t="s">
         <v>1225</v>
       </c>
@@ -22096,7 +22087,7 @@
         <v>✅</v>
       </c>
     </row>
-    <row r="960" ht="27.6" spans="1:5">
+    <row r="960" ht="27.6" customHeight="1" spans="1:5">
       <c r="A960" s="14" t="s">
         <v>1226</v>
       </c>
@@ -22119,186 +22110,186 @@
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="file:///C:/catalog/photos/Screenshot_122.png"/>
-    <hyperlink ref="C7" r:id="rId2" display="file:///C:/catalog/photos/Screenshot_125.png"/>
-    <hyperlink ref="C9" r:id="rId3" display="file:///C:/catalog/photos/Screenshot_102.png"/>
-    <hyperlink ref="C10" r:id="rId4" display="file:///C:/catalog/photos/Screenshot_108.png"/>
-    <hyperlink ref="C11" r:id="rId4" display="file:///C:/catalog/photos/Screenshot_108.png"/>
-    <hyperlink ref="C12" r:id="rId5" display="file:///C:/catalog/photos/Screenshot_106.png"/>
-    <hyperlink ref="C15" r:id="rId6" display="file:///C:/catalog/photos/Screenshot_114.png"/>
-    <hyperlink ref="C16" r:id="rId7" display="file:///C:/catalog/photos/Screenshot_116.png"/>
-    <hyperlink ref="C14" r:id="rId8" display="file:///C:/catalog/photos/Screenshot_115.png"/>
-    <hyperlink ref="C13" r:id="rId8" display="file:///C:/catalog/photos/Screenshot_115.png"/>
-    <hyperlink ref="C17" r:id="rId9" display="file:///C:/catalog/photos/Screenshot_99.png"/>
-    <hyperlink ref="C18" r:id="rId10" display="file:///C:/catalog/photos/Screenshot_117.png"/>
-    <hyperlink ref="C19" r:id="rId11" display="file:///C:/catalog/photos/Screenshot_179.png"/>
-    <hyperlink ref="C20" r:id="rId12" display="file:///C:/catalog/photos/Screenshot_181.png"/>
-    <hyperlink ref="C21" r:id="rId13" display="file:///C:/catalog/photos/Screenshot_183.png"/>
-    <hyperlink ref="C22" r:id="rId14" display="file:///C:/catalog/photos/Screenshot_180.png"/>
-    <hyperlink ref="C23" r:id="rId13" display="file:///C:/catalog/photos/Screenshot_183.png"/>
-    <hyperlink ref="C24" r:id="rId15" display="file:///C:/catalog/photos/Screenshot_182.png"/>
-    <hyperlink ref="C26" r:id="rId16" display="file:///C:/catalog/photos/Screenshot_119.png"/>
-    <hyperlink ref="C25" r:id="rId17" display="file:///C:/catalog/photos/Screenshot_118.png"/>
-    <hyperlink ref="C27" r:id="rId18" display="file:///C:/catalog/photos/Screenshot_112.png"/>
-    <hyperlink ref="C29" r:id="rId19" display="file:///C:/catalog/photos/Screenshot_113.png"/>
-    <hyperlink ref="C30" r:id="rId20" display="file:///C:/catalog/photos/Screenshot_110.png"/>
-    <hyperlink ref="C31" r:id="rId21" display="file:///C:/catalog/photos/089.png"/>
-    <hyperlink ref="C32" r:id="rId22" display="file:///C:/catalog/photos/090.png"/>
-    <hyperlink ref="C28" r:id="rId23" display="file:///C:/catalog/photos/Screenshot_188.png"/>
-    <hyperlink ref="C33" r:id="rId24" display="file:///C:/catalog/photos/Screenshot_189.png"/>
-    <hyperlink ref="C34" r:id="rId25" display="file:///C:/catalog/photos/Screenshot_84.png"/>
-    <hyperlink ref="C38" r:id="rId26" display="file:///C:/catalog/photos/Screenshot_192.png"/>
-    <hyperlink ref="C36" r:id="rId27" display="file:///C:/catalog/photos/Screenshot_190.png"/>
-    <hyperlink ref="C37" r:id="rId28" display="file:///C:/catalog/photos/Screenshot_191.png"/>
-    <hyperlink ref="C35" r:id="rId29" display="file:///C:/catalog/photos/Screenshot_28.png"/>
-    <hyperlink ref="C39" r:id="rId1" display="file:///C:/catalog/photos/Screenshot_122.png"/>
-    <hyperlink ref="C41" r:id="rId30" display="file:///C:/catalog/photos/031.png"/>
-    <hyperlink ref="C42" r:id="rId31" display="file:///C:/catalog/photos/032.png"/>
-    <hyperlink ref="C40" r:id="rId32" display="file:///C:/catalog/photos/033.png"/>
-    <hyperlink ref="C43" r:id="rId33" display="file:///C:/catalog/photos/Screenshot_71.png"/>
-    <hyperlink ref="C44" r:id="rId34" display="file:///C:/catalog/photos/Screenshot_193.png"/>
-    <hyperlink ref="C45" r:id="rId35" display="file:///C:/catalog/photos/Screenshot_32.png"/>
-    <hyperlink ref="C46" r:id="rId36" display="file:///C:/catalog/photos/Screenshot_34.png"/>
-    <hyperlink ref="C47" r:id="rId37" display="file:///C:/catalog/photos/Screenshot_194.png"/>
-    <hyperlink ref="C48" r:id="rId38" display="file:///C:/catalog/photos/Screenshot_195.png"/>
-    <hyperlink ref="C49" r:id="rId38" display="file:///C:/catalog/photos/Screenshot_195.png"/>
-    <hyperlink ref="C50" r:id="rId39" display="file:///C:/catalog/photos/Screenshot_196.png"/>
-    <hyperlink ref="C51" r:id="rId40" display="file:///C:/catalog/photos/Screenshot_197.png"/>
-    <hyperlink ref="C52" r:id="rId41" display="file:///C:/catalog/photos/Screenshot_198.png"/>
-    <hyperlink ref="C53" r:id="rId42" display="file:///C:/catalog/photos/Screenshot_199.png"/>
-    <hyperlink ref="C54" r:id="rId43" display="file:///C:/catalog/photos/Screenshot_200.png"/>
-    <hyperlink ref="C55" r:id="rId44" display="file:///C:/catalog/photos/Screenshot_91.png"/>
-    <hyperlink ref="C56" r:id="rId45" display="file:///C:/catalog/photos/Screenshot_89.png"/>
-    <hyperlink ref="C57" r:id="rId46" display="file:///C:/catalog/photos/096.png"/>
-    <hyperlink ref="C58" r:id="rId47" display="file:///C:/catalog/photos/Screenshot_22.png"/>
-    <hyperlink ref="C59" r:id="rId48" display="file:///C:/catalog/photos/Screenshot_23.png"/>
-    <hyperlink ref="C60" r:id="rId49" display="file:///C:/catalog/photos/Screenshot_24.png"/>
-    <hyperlink ref="C61" r:id="rId50" display="file:///C:/catalog/photos/Screenshot_172.png"/>
-    <hyperlink ref="C62" r:id="rId51" display="file:///C:/catalog/photos/Screenshot_201.png"/>
-    <hyperlink ref="C63" r:id="rId52" display="file:///C:/catalog/photos/Screenshot_202.png"/>
-    <hyperlink ref="C64" r:id="rId53" display="file:///C:/catalog/photos/Screenshot_171.png"/>
-    <hyperlink ref="C65" r:id="rId54" display="file:///C:/catalog/photos/Screenshot_163.png"/>
-    <hyperlink ref="C68" r:id="rId55" display="file:///C:/catalog/photos/Screenshot_154.png"/>
-    <hyperlink ref="C67" r:id="rId56" display="file:///C:/catalog/photos/Screenshot_150.png"/>
-    <hyperlink ref="C69" r:id="rId57" display="file:///C:/catalog/photos/Screenshot_155.png" tooltip="file:///C:/catalog/photos/Screenshot_155.png"/>
-    <hyperlink ref="C70" r:id="rId58" display="file:///C:/catalog/photos/Screenshot_174.png"/>
-    <hyperlink ref="C66" r:id="rId59" display="file:///C:/catalog/photos/016.png"/>
-    <hyperlink ref="C71" r:id="rId60" display="file:///C:/catalog/photos/Screenshot_135.png&#10;" tooltip="file:///C:/catalog/photos/Screenshot_135.png&#10;"/>
-    <hyperlink ref="C72" r:id="rId61" display="file:///C:/catalog/photos/Screenshot_130.png"/>
-    <hyperlink ref="C73" r:id="rId62" display="file:///C:/catalog/photos/Screenshot_132.png"/>
-    <hyperlink ref="C74" r:id="rId63" display="file:///C:/catalog/photos/Screenshot_133.png"/>
-    <hyperlink ref="C75" r:id="rId63" display="file:///C:/catalog/photos/Screenshot_133.png"/>
-    <hyperlink ref="C76" r:id="rId64" display="file:///C:/catalog/photos/020.png"/>
-    <hyperlink ref="C78" r:id="rId65" display="file:///C:/catalog/photos/004.png"/>
-    <hyperlink ref="C77" r:id="rId66" display="file:///C:/catalog/photos/003.png"/>
-    <hyperlink ref="C79" r:id="rId67" display="file:///C:/catalog/photos/005.png"/>
-    <hyperlink ref="C856" r:id="rId68" display="file:///C:/catalog/photos/Screenshot_187.png"/>
-    <hyperlink ref="C857" r:id="rId69" display="file:///C:/catalog/photos/056.png"/>
-    <hyperlink ref="C858" r:id="rId70" display="file:///C:/catalog/photos/055.png"/>
-    <hyperlink ref="C859" r:id="rId71" display="file:///C:/catalog/photos/Screenshot_128.png"/>
-    <hyperlink ref="C860" r:id="rId72" display="file:///C:/catalog/photos/071.png"/>
-    <hyperlink ref="C861" r:id="rId73" display="file:///C:/catalog/photos/072.png"/>
-    <hyperlink ref="C862" r:id="rId74" display="file:///C:/catalog/photos/099.png"/>
-    <hyperlink ref="C863" r:id="rId75" display="file:///C:/catalog/photos/102.png"/>
-    <hyperlink ref="C864" r:id="rId76" display="file:///C:/catalog/photos/100.png"/>
-    <hyperlink ref="C865" r:id="rId77" display="file:///C:/catalog/photos/Screenshot_38.png"/>
-    <hyperlink ref="C866" r:id="rId78" display="file:///C:/catalog/photos/Screenshot_4.png"/>
-    <hyperlink ref="C867" r:id="rId79" display="file:///C:/catalog/photos/Screenshot_5.png"/>
-    <hyperlink ref="C868" r:id="rId80" display="file:///C:/catalog/photos/044.png" tooltip="file:///C:/catalog/photos/044.png"/>
-    <hyperlink ref="C869" r:id="rId81" display="file:///C:/catalog/photos/045.png"/>
-    <hyperlink ref="C870" r:id="rId82" display="file:///C:/catalog/photos/042.png"/>
-    <hyperlink ref="C871" r:id="rId83" display="file:///C:/catalog/photos/Screenshot_78.png"/>
-    <hyperlink ref="C872" r:id="rId84" display="file:///C:/catalog/photos/Screenshot_76.png"/>
-    <hyperlink ref="C873" r:id="rId85" display="file:///C:/catalog/photos/Screenshot_73.png"/>
-    <hyperlink ref="C874" r:id="rId86" display="file:///C:/catalog/photos/Screenshot_81.png"/>
-    <hyperlink ref="C877" r:id="rId87" display="file:///C:/catalog/photos/Screenshot_63.png"/>
-    <hyperlink ref="C878" r:id="rId88" display="file:///C:/catalog/photos/Screenshot_64.png"/>
-    <hyperlink ref="C876" r:id="rId89" display="file:///C:/catalog/photos/Screenshot_204.png"/>
-    <hyperlink ref="C875" r:id="rId90" display="file:///C:/catalog/photos/Screenshot_203.png"/>
-    <hyperlink ref="C879" r:id="rId91" display="file:///C:/catalog/photos/073.png"/>
-    <hyperlink ref="C880" r:id="rId92" display="file:///C:/catalog/photos/Screenshot_14.png"/>
-    <hyperlink ref="C881" r:id="rId93" display="file:///C:/catalog/photos/Screenshot_9.png"/>
-    <hyperlink ref="C883" r:id="rId94" display="file:///C:/catalog/photos/Screenshot_8.png"/>
-    <hyperlink ref="C882" r:id="rId95" display="file:///C:/catalog/photos/Screenshot_11.png"/>
-    <hyperlink ref="C884" r:id="rId96" display="file:///C:/catalog/photos/082.png"/>
-    <hyperlink ref="C885" r:id="rId97" display="file:///C:/catalog/photos/077.png"/>
-    <hyperlink ref="C886" r:id="rId98" display="file:///C:/catalog/photos/Screenshot_205.png"/>
-    <hyperlink ref="C887" r:id="rId99" display="file:///C:/catalog/photos/028.png"/>
-    <hyperlink ref="C888" r:id="rId100" display="file:///C:/catalog/photos/027.png"/>
-    <hyperlink ref="C889" r:id="rId101" display="file:///C:/catalog/photos/106.png"/>
-    <hyperlink ref="C890" r:id="rId102" display="file:///C:/catalog/photos/107.png"/>
-    <hyperlink ref="C892" r:id="rId103" display="file:///C:/catalog/photos/024.png"/>
-    <hyperlink ref="C894" r:id="rId104" display="file:///C:/catalog/photos/023.png"/>
-    <hyperlink ref="C891" r:id="rId105" display="file:///C:/catalog/photos/Screenshot_126.png"/>
-    <hyperlink ref="C893" r:id="rId106" display="file:///C:/catalog/photos/Screenshot_127.png"/>
-    <hyperlink ref="C895" r:id="rId107" display="file:///C:/catalog/photos/Screenshot_69.png"/>
-    <hyperlink ref="C896" r:id="rId108" display="file:///C:/catalog/photos/Screenshot_68.png"/>
-    <hyperlink ref="C897" r:id="rId109" display="file:///C:/catalog/photos/Screenshot_67.png"/>
-    <hyperlink ref="C898" r:id="rId110" display="file:///C:/catalog/photos/Screenshot_66.png"/>
-    <hyperlink ref="C899" r:id="rId111" display="file:///C:/catalog/photos/Screenshot_61.png"/>
-    <hyperlink ref="C900" r:id="rId112" display="file:///C:/catalog/photos/091.png"/>
-    <hyperlink ref="C901" r:id="rId113" display="file:///C:/catalog/photos/092.png"/>
-    <hyperlink ref="C902" r:id="rId114" display="file:///C:/catalog/photos/Screenshot_80.png"/>
-    <hyperlink ref="C903" r:id="rId115" display="file:///C:/catalog/photos/083.png"/>
-    <hyperlink ref="C904" r:id="rId116" display="file:///C:/catalog/photos/Screenshot_25.png"/>
-    <hyperlink ref="C905" r:id="rId117" display="file:///C:/catalog/photos/086.png"/>
-    <hyperlink ref="C906" r:id="rId118" display="file:///C:/catalog/photos/085.png"/>
-    <hyperlink ref="C907" r:id="rId119" display="file:///C:/catalog/photos/Screenshot_1.png"/>
-    <hyperlink ref="C908" r:id="rId120" display="file:///C:/catalog/photos/Screenshot_206.png"/>
-    <hyperlink ref="C909" r:id="rId121" display="file:///C:/catalog/photos/Screenshot_43.png"/>
-    <hyperlink ref="C910" r:id="rId121" display="file:///C:/catalog/photos/Screenshot_43.png"/>
-    <hyperlink ref="C911" r:id="rId122" display="file:///C:/catalog/photos/066.png"/>
-    <hyperlink ref="C912" r:id="rId122" display="file:///C:/catalog/photos/066.png"/>
-    <hyperlink ref="C913" r:id="rId122" display="file:///C:/catalog/photos/066.png"/>
-    <hyperlink ref="C914" r:id="rId123" display="file:///C:/catalog/photos/047.png"/>
-    <hyperlink ref="C916" r:id="rId124" display="file:///C:/catalog/photos/046.png"/>
-    <hyperlink ref="C915" r:id="rId125" display="file:///C:/catalog/photos/048.png" tooltip="file:///C:/catalog/photos/048.png"/>
-    <hyperlink ref="C917" r:id="rId126" display="file:///C:/catalog/photos/Screenshot_90.png"/>
-    <hyperlink ref="C918" r:id="rId127" display="file:///C:/catalog/photos/Screenshot_50.png"/>
-    <hyperlink ref="C919" r:id="rId128" display="file:///C:/catalog/photos/Screenshot_16.png"/>
-    <hyperlink ref="C920" r:id="rId129" display="file:///C:/catalog/photos/040.png"/>
-    <hyperlink ref="C921" r:id="rId130" display="file:///C:/catalog/photos/038.png"/>
-    <hyperlink ref="C922" r:id="rId131" display="file:///C:/catalog/photos/041.png"/>
-    <hyperlink ref="C923" r:id="rId77" display="file:///C:/catalog/photos/Screenshot_38.png"/>
-    <hyperlink ref="C924" r:id="rId132" display="file:///C:/catalog/photos/Screenshot_29.png"/>
-    <hyperlink ref="C925" r:id="rId133" display="file:///C:/catalog/photos/Screenshot_207.png"/>
-    <hyperlink ref="C926" r:id="rId134" display="file:///C:/catalog/photos/Screenshot_208.png"/>
-    <hyperlink ref="C927" r:id="rId135" display="file:///C:/catalog/photos/Screenshot_177.png"/>
-    <hyperlink ref="C928" r:id="rId136" display="file:///C:/catalog/photos/Screenshot_168.png"/>
-    <hyperlink ref="C929" r:id="rId137" display="file:///C:/catalog/photos/Screenshot_167.png"/>
-    <hyperlink ref="C930" r:id="rId138" display="file:///C:/catalog/photos/Screenshot_173.png&#10;"/>
-    <hyperlink ref="C931" r:id="rId139" display="file:///C:/catalog/photos/Screenshot_162.png"/>
-    <hyperlink ref="C932" r:id="rId140" display="file:///C:/catalog/photos/Screenshot_165.png"/>
-    <hyperlink ref="C933" r:id="rId141" display="file:///C:/catalog/photos/Screenshot_164.png"/>
-    <hyperlink ref="C934" r:id="rId142" display="file:///C:/catalog/photos/Screenshot_166.png" tooltip="file:///C:/catalog/photos/Screenshot_166.png"/>
-    <hyperlink ref="C935" r:id="rId142" display="file:///C:/catalog/photos/Screenshot_166.png"/>
-    <hyperlink ref="C937" r:id="rId143" display="file:///C:/catalog/photos/Screenshot_170.png" tooltip="file:///C:/catalog/photos/Screenshot_170.png"/>
-    <hyperlink ref="C936" r:id="rId144" display="file:///C:/catalog/photos/Screenshot_169.png"/>
-    <hyperlink ref="C938" r:id="rId99" display="file:///C:/catalog/photos/028.png"/>
-    <hyperlink ref="C939" r:id="rId145" display="file:///C:/catalog/photos/015.png"/>
-    <hyperlink ref="C940" r:id="rId57" display="file:///C:/catalog/photos/Screenshot_155.png"/>
-    <hyperlink ref="C941" r:id="rId146" display="file:///C:/catalog/photos/Screenshot_139.png"/>
-    <hyperlink ref="C942" r:id="rId147" display="file:///C:/catalog/photos/Screenshot_131.png"/>
-    <hyperlink ref="C943" r:id="rId148" display="file:///C:/catalog/photos/Screenshot_138.png"/>
-    <hyperlink ref="C944" r:id="rId149" display="file:///C:/catalog/photos/Screenshot_209.png"/>
-    <hyperlink ref="C945" r:id="rId63" display="file:///C:/catalog/photos/Screenshot_133.png" tooltip="file:///C:/catalog/photos/Screenshot_133.png"/>
-    <hyperlink ref="C946" r:id="rId62" display="file:///C:/catalog/photos/Screenshot_132.png"/>
-    <hyperlink ref="C947" r:id="rId150" display="file:///C:/catalog/photos/019.png"/>
-    <hyperlink ref="C949" r:id="rId151" display="file:///C:/catalog/photos/Screenshot_210.png"/>
-    <hyperlink ref="C948" r:id="rId152" display="file:///C:/catalog/photos/Screenshot_211.png"/>
-    <hyperlink ref="C951" r:id="rId153" display="file:///C:/catalog/photos/013.png"/>
-    <hyperlink ref="C950" r:id="rId154" display="file:///C:/catalog/photos/001.png"/>
-    <hyperlink ref="C952" r:id="rId155" display="file:///C:/catalog/photos/Screenshot_212.png"/>
-    <hyperlink ref="C953" r:id="rId156" display="file:///C:/catalog/photos/008.png"/>
-    <hyperlink ref="C954" r:id="rId157" display="file:///C:/catalog/photos/009.png"/>
-    <hyperlink ref="C955" r:id="rId158" display="file:///C:/catalog/photos/002.png"/>
-    <hyperlink ref="C956" r:id="rId159" display="file:///C:/catalog/photos/Screenshot_92.png"/>
-    <hyperlink ref="C957" r:id="rId160" display="file:///C:/catalog/photos/Screenshot_185.png"/>
-    <hyperlink ref="C958" r:id="rId161" display="file:///C:/catalog/photos/Screenshot_186.png"/>
-    <hyperlink ref="C959" r:id="rId150" display="file:///C:/catalog/photos/019.png"/>
-    <hyperlink ref="C6" r:id="rId162" display="file:///C:/catalog/photos/050.png"/>
-    <hyperlink ref="C5" r:id="rId162" display="file:///C:/catalog/photos/050.png"/>
-    <hyperlink ref="C4" r:id="rId163" display="file:///C:/catalog/photos/059.png"/>
+    <hyperlink ref="C4" r:id="rId1" display="059.png"/>
+    <hyperlink ref="C5" r:id="rId2" display="050.png"/>
+    <hyperlink ref="C6" r:id="rId2" display="050.png"/>
+    <hyperlink ref="C7" r:id="rId3" display="Screenshot_125.png"/>
+    <hyperlink ref="C8" r:id="rId4" display="Screenshot_122.png"/>
+    <hyperlink ref="C9" r:id="rId5" display="Screenshot_102.png"/>
+    <hyperlink ref="C10" r:id="rId6" display="Screenshot_108.png"/>
+    <hyperlink ref="C11" r:id="rId6" display="Screenshot_108.png"/>
+    <hyperlink ref="C12" r:id="rId7" display="Screenshot_106.png"/>
+    <hyperlink ref="C13" r:id="rId8" display="Screenshot_115.png"/>
+    <hyperlink ref="C14" r:id="rId8" display="Screenshot_115.png"/>
+    <hyperlink ref="C15" r:id="rId9" display="Screenshot_114.png"/>
+    <hyperlink ref="C16" r:id="rId10" display="Screenshot_116.png"/>
+    <hyperlink ref="C17" r:id="rId11" display="Screenshot_99.png"/>
+    <hyperlink ref="C18" r:id="rId12" display="Screenshot_117.png"/>
+    <hyperlink ref="C19" r:id="rId13" display="Screenshot_179.png"/>
+    <hyperlink ref="C20" r:id="rId14" display="Screenshot_181.png"/>
+    <hyperlink ref="C21" r:id="rId15" display="Screenshot_183.png"/>
+    <hyperlink ref="C22" r:id="rId16" display="Screenshot_180.png"/>
+    <hyperlink ref="C23" r:id="rId15" display="Screenshot_183.png"/>
+    <hyperlink ref="C24" r:id="rId17" display="Screenshot_182.png"/>
+    <hyperlink ref="C25" r:id="rId18" display="Screenshot_118.png"/>
+    <hyperlink ref="C26" r:id="rId19" display="Screenshot_119.png"/>
+    <hyperlink ref="C27" r:id="rId20" display="Screenshot_112.png"/>
+    <hyperlink ref="C28" r:id="rId21" display="Screenshot_188.png"/>
+    <hyperlink ref="C29" r:id="rId22" display="Screenshot_113.png"/>
+    <hyperlink ref="C30" r:id="rId23" display="Screenshot_110.png"/>
+    <hyperlink ref="C31" r:id="rId24" display="089.png"/>
+    <hyperlink ref="C32" r:id="rId25" display="090.png"/>
+    <hyperlink ref="C33" r:id="rId26" display="Screenshot_189.png"/>
+    <hyperlink ref="C34" r:id="rId27" display="Screenshot_84.png"/>
+    <hyperlink ref="C35" r:id="rId28" display="Screenshot_28.png"/>
+    <hyperlink ref="C36" r:id="rId29" display="Screenshot_190.png"/>
+    <hyperlink ref="C37" r:id="rId30" display="Screenshot_191.png"/>
+    <hyperlink ref="C38" r:id="rId31" display="Screenshot_192.png"/>
+    <hyperlink ref="C39" r:id="rId4" display="Screenshot_122.png"/>
+    <hyperlink ref="C40" r:id="rId32" display="033.png"/>
+    <hyperlink ref="C41" r:id="rId33" display="031.png"/>
+    <hyperlink ref="C42" r:id="rId34" display="032.png"/>
+    <hyperlink ref="C43" r:id="rId35" display="Screenshot_71.png"/>
+    <hyperlink ref="C44" r:id="rId36" display="Screenshot_193.png"/>
+    <hyperlink ref="C45" r:id="rId37" display="Screenshot_32.png"/>
+    <hyperlink ref="C46" r:id="rId38" display="Screenshot_34.png"/>
+    <hyperlink ref="C47" r:id="rId39" display="Screenshot_194.png"/>
+    <hyperlink ref="C48" r:id="rId40" display="Screenshot_195.png"/>
+    <hyperlink ref="C49" r:id="rId40" display="Screenshot_195.png"/>
+    <hyperlink ref="C50" r:id="rId41" display="Screenshot_196.png"/>
+    <hyperlink ref="C51" r:id="rId42" display="Screenshot_197.png"/>
+    <hyperlink ref="C52" r:id="rId43" display="Screenshot_198.png"/>
+    <hyperlink ref="C53" r:id="rId44" display="Screenshot_199.png"/>
+    <hyperlink ref="C54" r:id="rId45" display="Screenshot_200.png"/>
+    <hyperlink ref="C55" r:id="rId46" display="Screenshot_91.png"/>
+    <hyperlink ref="C56" r:id="rId47" display="Screenshot_89.png"/>
+    <hyperlink ref="C57" r:id="rId48" display="096.png"/>
+    <hyperlink ref="C58" r:id="rId49" display="Screenshot_22.png"/>
+    <hyperlink ref="C59" r:id="rId50" display="Screenshot_23.png"/>
+    <hyperlink ref="C60" r:id="rId51" display="Screenshot_24.png"/>
+    <hyperlink ref="C61" r:id="rId52" display="Screenshot_172.png"/>
+    <hyperlink ref="C62" r:id="rId53" display="Screenshot_201.png"/>
+    <hyperlink ref="C63" r:id="rId54" display="Screenshot_202.png"/>
+    <hyperlink ref="C64" r:id="rId55" display="Screenshot_171.png"/>
+    <hyperlink ref="C65" r:id="rId56" display="Screenshot_163.png"/>
+    <hyperlink ref="C66" r:id="rId57" display="016.png"/>
+    <hyperlink ref="C67" r:id="rId58" display="Screenshot_150.png"/>
+    <hyperlink ref="C68" r:id="rId59" display="Screenshot_154.png"/>
+    <hyperlink ref="C69" r:id="rId60" display="Screenshot_155.png" tooltip="file:///C:/catalog/photos/Screenshot_155.png"/>
+    <hyperlink ref="C70" r:id="rId61" display="Screenshot_174.png"/>
+    <hyperlink ref="C71" r:id="rId62" display="Screenshot_135.png" tooltip="file:///C:/catalog/photos/Screenshot_135.png&#10;"/>
+    <hyperlink ref="C72" r:id="rId63" display="Screenshot_130.png"/>
+    <hyperlink ref="C73" r:id="rId64" display="Screenshot_132.png"/>
+    <hyperlink ref="C74" r:id="rId65" display="Screenshot_133.png"/>
+    <hyperlink ref="C75" r:id="rId65" display="Screenshot_133.png"/>
+    <hyperlink ref="C76" r:id="rId66" display="020.png"/>
+    <hyperlink ref="C77" r:id="rId67" display="003.png"/>
+    <hyperlink ref="C78" r:id="rId68" display="004.png"/>
+    <hyperlink ref="C79" r:id="rId69" display="005.png"/>
+    <hyperlink ref="C856" r:id="rId70" display="Screenshot_187.png"/>
+    <hyperlink ref="C857" r:id="rId71" display="056.png"/>
+    <hyperlink ref="C858" r:id="rId72" display="055.png"/>
+    <hyperlink ref="C859" r:id="rId73" display="Screenshot_128.png"/>
+    <hyperlink ref="C860" r:id="rId74" display="071.png"/>
+    <hyperlink ref="C861" r:id="rId75" display="072.png"/>
+    <hyperlink ref="C862" r:id="rId76" display="099.png"/>
+    <hyperlink ref="C863" r:id="rId77" display="102.png"/>
+    <hyperlink ref="C864" r:id="rId78" display="100.png"/>
+    <hyperlink ref="C865" r:id="rId79" display="Screenshot_38.png"/>
+    <hyperlink ref="C866" r:id="rId80" display="Screenshot_4.png"/>
+    <hyperlink ref="C867" r:id="rId81" display="Screenshot_5.png"/>
+    <hyperlink ref="C868" r:id="rId82" display="044.png" tooltip="file:///C:/catalog/photos/044.png"/>
+    <hyperlink ref="C869" r:id="rId83" display="045.png"/>
+    <hyperlink ref="C870" r:id="rId84" display="042.png"/>
+    <hyperlink ref="C871" r:id="rId85" display="Screenshot_78.png"/>
+    <hyperlink ref="C872" r:id="rId86" display="Screenshot_76.png"/>
+    <hyperlink ref="C873" r:id="rId87" display="Screenshot_73.png"/>
+    <hyperlink ref="C874" r:id="rId88" display="Screenshot_81.png"/>
+    <hyperlink ref="C875" r:id="rId89" display="Screenshot_203.png"/>
+    <hyperlink ref="C876" r:id="rId90" display="Screenshot_204.png"/>
+    <hyperlink ref="C877" r:id="rId91" display="Screenshot_63.png"/>
+    <hyperlink ref="C878" r:id="rId92" display="Screenshot_64.png"/>
+    <hyperlink ref="C879" r:id="rId93" display="073.png"/>
+    <hyperlink ref="C880" r:id="rId94" display="Screenshot_14.png"/>
+    <hyperlink ref="C881" r:id="rId95" display="Screenshot_9.png"/>
+    <hyperlink ref="C882" r:id="rId96" display="Screenshot_11.png"/>
+    <hyperlink ref="C883" r:id="rId97" display="Screenshot_8.png"/>
+    <hyperlink ref="C884" r:id="rId98" display="082.png"/>
+    <hyperlink ref="C885" r:id="rId99" display="077.png"/>
+    <hyperlink ref="C886" r:id="rId100" display="Screenshot_205.png"/>
+    <hyperlink ref="C887" r:id="rId101" display="028.png"/>
+    <hyperlink ref="C888" r:id="rId102" display="027.png"/>
+    <hyperlink ref="C889" r:id="rId103" display="106.png"/>
+    <hyperlink ref="C890" r:id="rId104" display="107.png"/>
+    <hyperlink ref="C891" r:id="rId105" display="Screenshot_126.png"/>
+    <hyperlink ref="C892" r:id="rId106" display="024.png"/>
+    <hyperlink ref="C893" r:id="rId107" display="Screenshot_127.png"/>
+    <hyperlink ref="C894" r:id="rId108" display="023.png"/>
+    <hyperlink ref="C895" r:id="rId109" display="Screenshot_69.png"/>
+    <hyperlink ref="C896" r:id="rId110" display="Screenshot_68.png"/>
+    <hyperlink ref="C897" r:id="rId111" display="Screenshot_67.png"/>
+    <hyperlink ref="C898" r:id="rId112" display="Screenshot_66.png"/>
+    <hyperlink ref="C899" r:id="rId113" display="Screenshot_61.png"/>
+    <hyperlink ref="C900" r:id="rId114" display="091.png"/>
+    <hyperlink ref="C901" r:id="rId115" display="092.png"/>
+    <hyperlink ref="C902" r:id="rId116" display="Screenshot_80.png"/>
+    <hyperlink ref="C903" r:id="rId117" display="083.png"/>
+    <hyperlink ref="C904" r:id="rId118" display="Screenshot_25.png"/>
+    <hyperlink ref="C905" r:id="rId119" display="086.png"/>
+    <hyperlink ref="C906" r:id="rId120" display="085.png"/>
+    <hyperlink ref="C907" r:id="rId121" display="Screenshot_1.png"/>
+    <hyperlink ref="C908" r:id="rId122" display="Screenshot_206.png"/>
+    <hyperlink ref="C909" r:id="rId123" display="Screenshot_43.png"/>
+    <hyperlink ref="C910" r:id="rId123" display="Screenshot_43.png"/>
+    <hyperlink ref="C911" r:id="rId124" display="066.png"/>
+    <hyperlink ref="C912" r:id="rId124" display="066.png"/>
+    <hyperlink ref="C913" r:id="rId124" display="066.png"/>
+    <hyperlink ref="C914" r:id="rId125" display="047.png"/>
+    <hyperlink ref="C915" r:id="rId126" display="048.png" tooltip="file:///C:/catalog/photos/048.png"/>
+    <hyperlink ref="C916" r:id="rId127" display="046.png"/>
+    <hyperlink ref="C917" r:id="rId128" display="Screenshot_90.png"/>
+    <hyperlink ref="C918" r:id="rId129" display="Screenshot_50.png"/>
+    <hyperlink ref="C919" r:id="rId130" display="Screenshot_16.png"/>
+    <hyperlink ref="C920" r:id="rId131" display="040.png"/>
+    <hyperlink ref="C921" r:id="rId132" display="038.png"/>
+    <hyperlink ref="C922" r:id="rId133" display="041.png"/>
+    <hyperlink ref="C923" r:id="rId79" display="Screenshot_38.png"/>
+    <hyperlink ref="C924" r:id="rId134" display="Screenshot_29.png"/>
+    <hyperlink ref="C925" r:id="rId135" display="Screenshot_207.png"/>
+    <hyperlink ref="C926" r:id="rId136" display="Screenshot_208.png"/>
+    <hyperlink ref="C927" r:id="rId137" display="Screenshot_177.png"/>
+    <hyperlink ref="C928" r:id="rId138" display="Screenshot_168.png"/>
+    <hyperlink ref="C929" r:id="rId139" display="Screenshot_167.png"/>
+    <hyperlink ref="C930" r:id="rId140" display="Screenshot_173.png"/>
+    <hyperlink ref="C931" r:id="rId141" display="Screenshot_162.png"/>
+    <hyperlink ref="C932" r:id="rId142" display="Screenshot_165.png"/>
+    <hyperlink ref="C933" r:id="rId143" display="Screenshot_164.png"/>
+    <hyperlink ref="C934" r:id="rId144" display="Screenshot_166.png" tooltip="file:///C:/catalog/photos/Screenshot_166.png"/>
+    <hyperlink ref="C935" r:id="rId144" display="Screenshot_166.png"/>
+    <hyperlink ref="C936" r:id="rId145" display="Screenshot_169.png"/>
+    <hyperlink ref="C937" r:id="rId146" display="Screenshot_170.png" tooltip="file:///C:/catalog/photos/Screenshot_170.png"/>
+    <hyperlink ref="C938" r:id="rId101" display="028.png"/>
+    <hyperlink ref="C939" r:id="rId147" display="015.png"/>
+    <hyperlink ref="C940" r:id="rId60" display="Screenshot_155.png"/>
+    <hyperlink ref="C941" r:id="rId148" display="Screenshot_139.png"/>
+    <hyperlink ref="C942" r:id="rId149" display="Screenshot_131.png"/>
+    <hyperlink ref="C943" r:id="rId150" display="Screenshot_138.png"/>
+    <hyperlink ref="C944" r:id="rId151" display="Screenshot_209.png"/>
+    <hyperlink ref="C945" r:id="rId65" display="Screenshot_133.png" tooltip="file:///C:/catalog/photos/Screenshot_133.png"/>
+    <hyperlink ref="C946" r:id="rId64" display="Screenshot_132.png"/>
+    <hyperlink ref="C947" r:id="rId152" display="019.png"/>
+    <hyperlink ref="C948" r:id="rId153" display="Screenshot_211.png"/>
+    <hyperlink ref="C949" r:id="rId154" display="Screenshot_210.png"/>
+    <hyperlink ref="C950" r:id="rId155" display="001.png"/>
+    <hyperlink ref="C951" r:id="rId156" display="013.png"/>
+    <hyperlink ref="C952" r:id="rId157" display="Screenshot_212.png"/>
+    <hyperlink ref="C953" r:id="rId158" display="008.png"/>
+    <hyperlink ref="C954" r:id="rId159" display="009.png"/>
+    <hyperlink ref="C955" r:id="rId160" display="002.png"/>
+    <hyperlink ref="C956" r:id="rId161" display="Screenshot_92.png"/>
+    <hyperlink ref="C957" r:id="rId162" display="Screenshot_185.png"/>
+    <hyperlink ref="C958" r:id="rId163" display="Screenshot_186.png"/>
+    <hyperlink ref="C959" r:id="rId152" display="019.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/photo_manual.xlsx
+++ b/photo_manual.xlsx
@@ -1219,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1298"/>
+  <dimension ref="A1:E1309"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -23809,1513 +23809,1513 @@
       </c>
     </row>
     <row r="1034">
-      <c r="A1034" s="26" t="inlineStr">
+      <c r="A1034" s="30" t="inlineStr">
         <is>
           <t>Акконд батончик "Splash" жареный арахис и карамель конфета 40г/40</t>
         </is>
       </c>
-      <c r="B1034" s="26" t="inlineStr">
+      <c r="B1034" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1034" s="26" t="inlineStr"/>
+      <c r="C1034" s="30" t="inlineStr"/>
       <c r="D1034" s="27" t="inlineStr"/>
-      <c r="E1034" s="26">
+      <c r="E1034" s="30">
         <f>IF(C1034&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1035">
-      <c r="A1035" s="28" t="inlineStr">
+      <c r="A1035" s="31" t="inlineStr">
         <is>
           <t>Акконд батончик Фитси мультизлаки и курага 22г/150</t>
         </is>
       </c>
-      <c r="B1035" s="28" t="inlineStr">
+      <c r="B1035" s="31" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1035" s="28" t="inlineStr"/>
+      <c r="C1035" s="31" t="inlineStr"/>
       <c r="D1035" s="29" t="inlineStr"/>
-      <c r="E1035" s="28">
+      <c r="E1035" s="31">
         <f>IF(C1035&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1036">
-      <c r="A1036" s="26" t="inlineStr">
+      <c r="A1036" s="30" t="inlineStr">
         <is>
           <t>Акконд шоколад Шоко-кроко с молочной начинкой 28г/50</t>
         </is>
       </c>
-      <c r="B1036" s="26" t="inlineStr">
+      <c r="B1036" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1036" s="26" t="inlineStr"/>
+      <c r="C1036" s="30" t="inlineStr"/>
       <c r="D1036" s="27" t="inlineStr"/>
-      <c r="E1036" s="26">
+      <c r="E1036" s="30">
         <f>IF(C1036&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1037">
-      <c r="A1037" s="28" t="inlineStr">
+      <c r="A1037" s="31" t="inlineStr">
         <is>
           <t>Батончик Баунти 55г/32шт (6)</t>
         </is>
       </c>
-      <c r="B1037" s="28" t="inlineStr">
+      <c r="B1037" s="31" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1037" s="28" t="inlineStr"/>
+      <c r="C1037" s="31" t="inlineStr"/>
       <c r="D1037" s="29" t="inlineStr"/>
-      <c r="E1037" s="28">
+      <c r="E1037" s="31">
         <f>IF(C1037&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1038">
-      <c r="A1038" s="26" t="inlineStr">
+      <c r="A1038" s="30" t="inlineStr">
         <is>
           <t>Батончик КитКат Темный 41.5г/24шт №23</t>
         </is>
       </c>
-      <c r="B1038" s="26" t="inlineStr">
+      <c r="B1038" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1038" s="26" t="inlineStr"/>
+      <c r="C1038" s="30" t="inlineStr"/>
       <c r="D1038" s="27" t="inlineStr"/>
-      <c r="E1038" s="26">
+      <c r="E1038" s="30">
         <f>IF(C1038&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1039">
-      <c r="A1039" s="28" t="inlineStr">
+      <c r="A1039" s="31" t="inlineStr">
         <is>
           <t>Батончик Пикник Биг 76г/30шт</t>
         </is>
       </c>
-      <c r="B1039" s="28" t="inlineStr">
+      <c r="B1039" s="31" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1039" s="28" t="inlineStr"/>
+      <c r="C1039" s="31" t="inlineStr"/>
       <c r="D1039" s="29" t="inlineStr"/>
-      <c r="E1039" s="28">
+      <c r="E1039" s="31">
         <f>IF(C1039&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1040">
-      <c r="A1040" s="26" t="inlineStr">
+      <c r="A1040" s="30" t="inlineStr">
         <is>
           <t>Батончик Твикс Экстра солёная карамель 82г/24шт</t>
         </is>
       </c>
-      <c r="B1040" s="26" t="inlineStr">
+      <c r="B1040" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1040" s="26" t="inlineStr"/>
+      <c r="C1040" s="30" t="inlineStr"/>
       <c r="D1040" s="27" t="inlineStr"/>
-      <c r="E1040" s="26">
+      <c r="E1040" s="30">
         <f>IF(C1040&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1041">
-      <c r="A1041" s="28" t="inlineStr">
+      <c r="A1041" s="31" t="inlineStr">
         <is>
           <t>Киндер Буэно в БЕЛОМ ШОКОЛАДЕ 43г/30шт</t>
         </is>
       </c>
-      <c r="B1041" s="28" t="inlineStr">
+      <c r="B1041" s="31" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1041" s="28" t="inlineStr"/>
+      <c r="C1041" s="31" t="inlineStr"/>
       <c r="D1041" s="29" t="inlineStr"/>
-      <c r="E1041" s="28">
+      <c r="E1041" s="31">
         <f>IF(C1041&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1042">
-      <c r="A1042" s="26" t="inlineStr">
+      <c r="A1042" s="30" t="inlineStr">
         <is>
           <t>Киндер Сюрприз 20г/36 Зайчик</t>
         </is>
       </c>
-      <c r="B1042" s="26" t="inlineStr">
+      <c r="B1042" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1042" s="26" t="inlineStr"/>
+      <c r="C1042" s="30" t="inlineStr"/>
       <c r="D1042" s="27" t="inlineStr"/>
-      <c r="E1042" s="26">
+      <c r="E1042" s="30">
         <f>IF(C1042&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1043">
-      <c r="A1043" s="28" t="inlineStr">
+      <c r="A1043" s="31" t="inlineStr">
         <is>
           <t>Киндер Сюрприз 36\20г Миссия</t>
         </is>
       </c>
-      <c r="B1043" s="28" t="inlineStr">
+      <c r="B1043" s="31" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1043" s="28" t="inlineStr"/>
+      <c r="C1043" s="31" t="inlineStr"/>
       <c r="D1043" s="29" t="inlineStr"/>
-      <c r="E1043" s="28">
+      <c r="E1043" s="31">
         <f>IF(C1043&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1044">
-      <c r="A1044" s="26" t="inlineStr">
+      <c r="A1044" s="30" t="inlineStr">
         <is>
           <t>Киндер Сюрприз База 20/36шт</t>
         </is>
       </c>
-      <c r="B1044" s="26" t="inlineStr">
+      <c r="B1044" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1044" s="26" t="inlineStr"/>
+      <c r="C1044" s="30" t="inlineStr"/>
       <c r="D1044" s="27" t="inlineStr"/>
-      <c r="E1044" s="26">
+      <c r="E1044" s="30">
         <f>IF(C1044&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1045">
-      <c r="A1045" s="28" t="inlineStr">
+      <c r="A1045" s="31" t="inlineStr">
         <is>
           <t>Нап. Let's Be ЧАЙ Латте 240мл х 30</t>
         </is>
       </c>
-      <c r="B1045" s="28" t="inlineStr">
+      <c r="B1045" s="31" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1045" s="28" t="inlineStr"/>
+      <c r="C1045" s="31" t="inlineStr"/>
       <c r="D1045" s="29" t="inlineStr"/>
-      <c r="E1045" s="28">
+      <c r="E1045" s="31">
         <f>IF(C1045&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1046">
-      <c r="A1046" s="26" t="inlineStr">
+      <c r="A1046" s="30" t="inlineStr">
         <is>
           <t>Шоколад Милка Цельный орех Whole Nuts 95г/17шт</t>
         </is>
       </c>
-      <c r="B1046" s="26" t="inlineStr">
+      <c r="B1046" s="30" t="inlineStr">
         <is>
           <t>Батончики и шоколад</t>
         </is>
       </c>
-      <c r="C1046" s="26" t="inlineStr"/>
+      <c r="C1046" s="30" t="inlineStr"/>
       <c r="D1046" s="27" t="inlineStr"/>
-      <c r="E1046" s="26">
+      <c r="E1046" s="30">
         <f>IF(C1046&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1047">
-      <c r="A1047" s="28" t="inlineStr">
+      <c r="A1047" s="31" t="inlineStr">
         <is>
           <t>Дет. Марм. Хинкалик с джемом 13г/30 (12)</t>
         </is>
       </c>
-      <c r="B1047" s="28" t="inlineStr">
+      <c r="B1047" s="31" t="inlineStr">
         <is>
           <t>Детское</t>
         </is>
       </c>
-      <c r="C1047" s="28" t="inlineStr"/>
+      <c r="C1047" s="31" t="inlineStr"/>
       <c r="D1047" s="29" t="inlineStr"/>
-      <c r="E1047" s="28">
+      <c r="E1047" s="31">
         <f>IF(C1047&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1048">
-      <c r="A1048" s="26" t="inlineStr">
+      <c r="A1048" s="30" t="inlineStr">
         <is>
           <t>Акконд вафли фас. Бравер какао и молоко. 250г/6</t>
         </is>
       </c>
-      <c r="B1048" s="26" t="inlineStr">
+      <c r="B1048" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1048" s="26" t="inlineStr"/>
+      <c r="C1048" s="30" t="inlineStr"/>
       <c r="D1048" s="27" t="inlineStr"/>
-      <c r="E1048" s="26">
+      <c r="E1048" s="30">
         <f>IF(C1048&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1049">
-      <c r="A1049" s="28" t="inlineStr">
+      <c r="A1049" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты "Splash" жареный арахис и карамель 1/4</t>
         </is>
       </c>
-      <c r="B1049" s="28" t="inlineStr">
+      <c r="B1049" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1049" s="28" t="inlineStr"/>
+      <c r="C1049" s="31" t="inlineStr"/>
       <c r="D1049" s="29" t="inlineStr"/>
-      <c r="E1049" s="28">
+      <c r="E1049" s="31">
         <f>IF(C1049&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1050">
-      <c r="A1050" s="26" t="inlineStr">
+      <c r="A1050" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты "Splash" жареный арахис карамель и нуга MEGA 1/4</t>
         </is>
       </c>
-      <c r="B1050" s="26" t="inlineStr">
+      <c r="B1050" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1050" s="26" t="inlineStr"/>
+      <c r="C1050" s="30" t="inlineStr"/>
       <c r="D1050" s="27" t="inlineStr"/>
-      <c r="E1050" s="26">
+      <c r="E1050" s="30">
         <f>IF(C1050&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1051">
-      <c r="A1051" s="28" t="inlineStr">
+      <c r="A1051" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Аккондовские с шок. вкусом вафли 1/4</t>
         </is>
       </c>
-      <c r="B1051" s="28" t="inlineStr">
+      <c r="B1051" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1051" s="28" t="inlineStr"/>
+      <c r="C1051" s="31" t="inlineStr"/>
       <c r="D1051" s="29" t="inlineStr"/>
-      <c r="E1051" s="28">
+      <c r="E1051" s="31">
         <f>IF(C1051&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1052">
-      <c r="A1052" s="26" t="inlineStr">
+      <c r="A1052" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты желейные Отважный комарик со вкусом Вишни 1/4</t>
         </is>
       </c>
-      <c r="B1052" s="26" t="inlineStr">
+      <c r="B1052" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1052" s="26" t="inlineStr"/>
+      <c r="C1052" s="30" t="inlineStr"/>
       <c r="D1052" s="27" t="inlineStr"/>
-      <c r="E1052" s="26">
+      <c r="E1052" s="30">
         <f>IF(C1052&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1053">
-      <c r="A1053" s="28" t="inlineStr">
+      <c r="A1053" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты желейные Отважный комарик со вкусом Дыня-клубника 1/4</t>
         </is>
       </c>
-      <c r="B1053" s="28" t="inlineStr">
+      <c r="B1053" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1053" s="28" t="inlineStr"/>
+      <c r="C1053" s="31" t="inlineStr"/>
       <c r="D1053" s="29" t="inlineStr"/>
-      <c r="E1053" s="28">
+      <c r="E1053" s="31">
         <f>IF(C1053&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1054">
-      <c r="A1054" s="26" t="inlineStr">
+      <c r="A1054" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты желейные Отважный комарик со вкусом Клубника 1/4</t>
         </is>
       </c>
-      <c r="B1054" s="26" t="inlineStr">
+      <c r="B1054" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1054" s="26" t="inlineStr"/>
+      <c r="C1054" s="30" t="inlineStr"/>
       <c r="D1054" s="27" t="inlineStr"/>
-      <c r="E1054" s="26">
+      <c r="E1054" s="30">
         <f>IF(C1054&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1055">
-      <c r="A1055" s="28" t="inlineStr">
+      <c r="A1055" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Леди День курага 1/3</t>
         </is>
       </c>
-      <c r="B1055" s="28" t="inlineStr">
+      <c r="B1055" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1055" s="28" t="inlineStr"/>
+      <c r="C1055" s="31" t="inlineStr"/>
       <c r="D1055" s="29" t="inlineStr"/>
-      <c r="E1055" s="28">
+      <c r="E1055" s="31">
         <f>IF(C1055&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1056">
-      <c r="A1056" s="26" t="inlineStr">
+      <c r="A1056" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Леди День чернослив 1/3</t>
         </is>
       </c>
-      <c r="B1056" s="26" t="inlineStr">
+      <c r="B1056" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1056" s="26" t="inlineStr"/>
+      <c r="C1056" s="30" t="inlineStr"/>
       <c r="D1056" s="27" t="inlineStr"/>
-      <c r="E1056" s="26">
+      <c r="E1056" s="30">
         <f>IF(C1056&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1057">
-      <c r="A1057" s="28" t="inlineStr">
+      <c r="A1057" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Леди Ночь курага 1/3</t>
         </is>
       </c>
-      <c r="B1057" s="28" t="inlineStr">
+      <c r="B1057" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1057" s="28" t="inlineStr"/>
+      <c r="C1057" s="31" t="inlineStr"/>
       <c r="D1057" s="29" t="inlineStr"/>
-      <c r="E1057" s="28">
+      <c r="E1057" s="31">
         <f>IF(C1057&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1058">
-      <c r="A1058" s="26" t="inlineStr">
+      <c r="A1058" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Леди Ночь финики 1/3</t>
         </is>
       </c>
-      <c r="B1058" s="26" t="inlineStr">
+      <c r="B1058" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1058" s="26" t="inlineStr"/>
+      <c r="C1058" s="30" t="inlineStr"/>
       <c r="D1058" s="27" t="inlineStr"/>
-      <c r="E1058" s="26">
+      <c r="E1058" s="30">
         <f>IF(C1058&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1059">
-      <c r="A1059" s="28" t="inlineStr">
+      <c r="A1059" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Нямик 1/4кг</t>
         </is>
       </c>
-      <c r="B1059" s="28" t="inlineStr">
+      <c r="B1059" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1059" s="28" t="inlineStr"/>
+      <c r="C1059" s="31" t="inlineStr"/>
       <c r="D1059" s="29" t="inlineStr"/>
-      <c r="E1059" s="28">
+      <c r="E1059" s="31">
         <f>IF(C1059&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1060">
-      <c r="A1060" s="26" t="inlineStr">
+      <c r="A1060" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Птица дивная двухслойные в шоколадной глазури 1/4</t>
         </is>
       </c>
-      <c r="B1060" s="26" t="inlineStr">
+      <c r="B1060" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1060" s="26" t="inlineStr"/>
+      <c r="C1060" s="30" t="inlineStr"/>
       <c r="D1060" s="27" t="inlineStr"/>
-      <c r="E1060" s="26">
+      <c r="E1060" s="30">
         <f>IF(C1060&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1061">
-      <c r="A1061" s="28" t="inlineStr">
+      <c r="A1061" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Ричио 1/3</t>
         </is>
       </c>
-      <c r="B1061" s="28" t="inlineStr">
+      <c r="B1061" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1061" s="28" t="inlineStr"/>
+      <c r="C1061" s="31" t="inlineStr"/>
       <c r="D1061" s="29" t="inlineStr"/>
-      <c r="E1061" s="28">
+      <c r="E1061" s="31">
         <f>IF(C1061&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1062">
-      <c r="A1062" s="26" t="inlineStr">
+      <c r="A1062" s="30" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Ричио 1/3 пралинео</t>
         </is>
       </c>
-      <c r="B1062" s="26" t="inlineStr">
+      <c r="B1062" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1062" s="26" t="inlineStr"/>
+      <c r="C1062" s="30" t="inlineStr"/>
       <c r="D1062" s="27" t="inlineStr"/>
-      <c r="E1062" s="26">
+      <c r="E1062" s="30">
         <f>IF(C1062&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1063">
-      <c r="A1063" s="28" t="inlineStr">
+      <c r="A1063" s="31" t="inlineStr">
         <is>
           <t>Акконд вес. конфеты Шоко Бар с печеньем и карамелью  1/3</t>
         </is>
       </c>
-      <c r="B1063" s="28" t="inlineStr">
+      <c r="B1063" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1063" s="28" t="inlineStr"/>
+      <c r="C1063" s="31" t="inlineStr"/>
       <c r="D1063" s="29" t="inlineStr"/>
-      <c r="E1063" s="28">
+      <c r="E1063" s="31">
         <f>IF(C1063&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1064">
-      <c r="A1064" s="26" t="inlineStr">
+      <c r="A1064" s="30" t="inlineStr">
         <is>
           <t>Вес. конфеты ваф. Аленка 1/4кг</t>
         </is>
       </c>
-      <c r="B1064" s="26" t="inlineStr">
+      <c r="B1064" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1064" s="26" t="inlineStr"/>
+      <c r="C1064" s="30" t="inlineStr"/>
       <c r="D1064" s="27" t="inlineStr"/>
-      <c r="E1064" s="26">
+      <c r="E1064" s="30">
         <f>IF(C1064&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1065">
-      <c r="A1065" s="28" t="inlineStr">
+      <c r="A1065" s="31" t="inlineStr">
         <is>
           <t>Вес. конфеты мини Сникерс 1кг/7</t>
         </is>
       </c>
-      <c r="B1065" s="28" t="inlineStr">
+      <c r="B1065" s="31" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1065" s="28" t="inlineStr"/>
+      <c r="C1065" s="31" t="inlineStr"/>
       <c r="D1065" s="29" t="inlineStr"/>
-      <c r="E1065" s="28">
+      <c r="E1065" s="31">
         <f>IF(C1065&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1066">
-      <c r="A1066" s="26" t="inlineStr">
+      <c r="A1066" s="30" t="inlineStr">
         <is>
           <t>Вес. конфеты мини Твикс сол. кар. 1/7кг</t>
         </is>
       </c>
-      <c r="B1066" s="26" t="inlineStr">
+      <c r="B1066" s="30" t="inlineStr">
         <is>
           <t>Конфеты и печенье</t>
         </is>
       </c>
-      <c r="C1066" s="26" t="inlineStr"/>
+      <c r="C1066" s="30" t="inlineStr"/>
       <c r="D1066" s="27" t="inlineStr"/>
-      <c r="E1066" s="26">
+      <c r="E1066" s="30">
         <f>IF(C1066&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1067">
-      <c r="A1067" s="28" t="inlineStr">
+      <c r="A1067" s="31" t="inlineStr">
         <is>
           <t>Добрый Кола 1л\12</t>
         </is>
       </c>
-      <c r="B1067" s="28" t="inlineStr">
+      <c r="B1067" s="31" t="inlineStr">
         <is>
           <t>Напитки</t>
         </is>
       </c>
-      <c r="C1067" s="28" t="inlineStr"/>
+      <c r="C1067" s="31" t="inlineStr"/>
       <c r="D1067" s="29" t="inlineStr"/>
-      <c r="E1067" s="28">
+      <c r="E1067" s="31">
         <f>IF(C1067&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1068">
-      <c r="A1068" s="26" t="inlineStr">
+      <c r="A1068" s="30" t="inlineStr">
         <is>
           <t>Квас Жёлтая бочка 1.5\6</t>
         </is>
       </c>
-      <c r="B1068" s="26" t="inlineStr">
+      <c r="B1068" s="30" t="inlineStr">
         <is>
           <t>Напитки</t>
         </is>
       </c>
-      <c r="C1068" s="26" t="inlineStr"/>
+      <c r="C1068" s="30" t="inlineStr"/>
       <c r="D1068" s="27" t="inlineStr"/>
-      <c r="E1068" s="26">
+      <c r="E1068" s="30">
         <f>IF(C1068&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1069">
-      <c r="A1069" s="28" t="inlineStr">
+      <c r="A1069" s="31" t="inlineStr">
         <is>
           <t>Квас Жёлтая бочка 2.5/4</t>
         </is>
       </c>
-      <c r="B1069" s="28" t="inlineStr">
+      <c r="B1069" s="31" t="inlineStr">
         <is>
           <t>Напитки</t>
         </is>
       </c>
-      <c r="C1069" s="28" t="inlineStr"/>
+      <c r="C1069" s="31" t="inlineStr"/>
       <c r="D1069" s="29" t="inlineStr"/>
-      <c r="E1069" s="28">
+      <c r="E1069" s="31">
         <f>IF(C1069&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1070">
-      <c r="A1070" s="26" t="inlineStr">
+      <c r="A1070" s="30" t="inlineStr">
         <is>
           <t>Нап.кофейный негаз. Кофетайм 240мл х 30</t>
         </is>
       </c>
-      <c r="B1070" s="26" t="inlineStr">
+      <c r="B1070" s="30" t="inlineStr">
         <is>
           <t>Напитки</t>
         </is>
       </c>
-      <c r="C1070" s="26" t="inlineStr"/>
+      <c r="C1070" s="30" t="inlineStr"/>
       <c r="D1070" s="27" t="inlineStr"/>
-      <c r="E1070" s="26">
+      <c r="E1070" s="30">
         <f>IF(C1070&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1071">
-      <c r="A1071" s="28" t="inlineStr">
+      <c r="A1071" s="31" t="inlineStr">
         <is>
           <t>Ж/р Ментос ролл Pure Fresh Клубника 15,5г/24шт (12)</t>
         </is>
       </c>
-      <c r="B1071" s="28" t="inlineStr">
+      <c r="B1071" s="31" t="inlineStr">
         <is>
           <t>Прикассовое</t>
         </is>
       </c>
-      <c r="C1071" s="28" t="inlineStr"/>
+      <c r="C1071" s="31" t="inlineStr"/>
       <c r="D1071" s="29" t="inlineStr"/>
-      <c r="E1071" s="28">
+      <c r="E1071" s="31">
         <f>IF(C1071&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1072">
-      <c r="A1072" s="26" t="inlineStr">
+      <c r="A1072" s="30" t="inlineStr">
         <is>
           <t>Ж/р Ментос ролл Pure White Мята 15,5г/24шт (12)</t>
         </is>
       </c>
-      <c r="B1072" s="26" t="inlineStr">
+      <c r="B1072" s="30" t="inlineStr">
         <is>
           <t>Прикассовое</t>
         </is>
       </c>
-      <c r="C1072" s="26" t="inlineStr"/>
+      <c r="C1072" s="30" t="inlineStr"/>
       <c r="D1072" s="27" t="inlineStr"/>
-      <c r="E1072" s="26">
+      <c r="E1072" s="30">
         <f>IF(C1072&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1073">
-      <c r="A1073" s="28" t="inlineStr">
+      <c r="A1073" s="31" t="inlineStr">
         <is>
           <t>Ж/р Ментос ролл Pure White Свежая мята 15,5г/24шт (12)</t>
         </is>
       </c>
-      <c r="B1073" s="28" t="inlineStr">
+      <c r="B1073" s="31" t="inlineStr">
         <is>
           <t>Прикассовое</t>
         </is>
       </c>
-      <c r="C1073" s="28" t="inlineStr"/>
+      <c r="C1073" s="31" t="inlineStr"/>
       <c r="D1073" s="29" t="inlineStr"/>
-      <c r="E1073" s="28">
+      <c r="E1073" s="31">
         <f>IF(C1073&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1074">
-      <c r="A1074" s="26" t="inlineStr">
+      <c r="A1074" s="30" t="inlineStr">
         <is>
           <t>Ж/р Орбит Белос.Нежная Мята 13,6г/30 (20)</t>
         </is>
       </c>
-      <c r="B1074" s="26" t="inlineStr">
+      <c r="B1074" s="30" t="inlineStr">
         <is>
           <t>Прикассовое</t>
         </is>
       </c>
-      <c r="C1074" s="26" t="inlineStr"/>
+      <c r="C1074" s="30" t="inlineStr"/>
       <c r="D1074" s="27" t="inlineStr"/>
-      <c r="E1074" s="26">
+      <c r="E1074" s="30">
         <f>IF(C1074&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1075">
-      <c r="A1075" s="28" t="inlineStr">
+      <c r="A1075" s="31" t="inlineStr">
         <is>
           <t>Ж/р Орбит Клубника-Банан 13,6г/30 (20)</t>
         </is>
       </c>
-      <c r="B1075" s="28" t="inlineStr">
+      <c r="B1075" s="31" t="inlineStr">
         <is>
           <t>Прикассовое</t>
         </is>
       </c>
-      <c r="C1075" s="28" t="inlineStr"/>
+      <c r="C1075" s="31" t="inlineStr"/>
       <c r="D1075" s="29" t="inlineStr"/>
-      <c r="E1075" s="28">
+      <c r="E1075" s="31">
         <f>IF(C1075&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1076">
-      <c r="A1076" s="26" t="inlineStr">
+      <c r="A1076" s="30" t="inlineStr">
         <is>
           <t>Ж/р Орбит Сладкая Мята 13,6г/30 (20)</t>
         </is>
       </c>
-      <c r="B1076" s="26" t="inlineStr">
+      <c r="B1076" s="30" t="inlineStr">
         <is>
           <t>Прикассовое</t>
         </is>
       </c>
-      <c r="C1076" s="26" t="inlineStr"/>
+      <c r="C1076" s="30" t="inlineStr"/>
       <c r="D1076" s="27" t="inlineStr"/>
-      <c r="E1076" s="26">
+      <c r="E1076" s="30">
         <f>IF(C1076&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1077">
-      <c r="A1077" s="28" t="inlineStr">
+      <c r="A1077" s="31" t="inlineStr">
         <is>
           <t>Гренкино Стак. 50г/32 Жёлтый полосатик</t>
         </is>
       </c>
-      <c r="B1077" s="28" t="inlineStr">
+      <c r="B1077" s="31" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1077" s="28" t="inlineStr"/>
+      <c r="C1077" s="31" t="inlineStr"/>
       <c r="D1077" s="29" t="inlineStr"/>
-      <c r="E1077" s="28">
+      <c r="E1077" s="31">
         <f>IF(C1077&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1078">
-      <c r="A1078" s="26" t="inlineStr">
+      <c r="A1078" s="30" t="inlineStr">
         <is>
           <t>Орехи Фисташка Иран 1кг</t>
         </is>
       </c>
-      <c r="B1078" s="26" t="inlineStr">
+      <c r="B1078" s="30" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1078" s="26" t="inlineStr"/>
+      <c r="C1078" s="30" t="inlineStr"/>
       <c r="D1078" s="27" t="inlineStr"/>
-      <c r="E1078" s="26">
+      <c r="E1078" s="30">
         <f>IF(C1078&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1079">
-      <c r="A1079" s="28" t="inlineStr">
+      <c r="A1079" s="31" t="inlineStr">
         <is>
           <t>Орехи Фисташка Калифорния Премиум 1 кг</t>
         </is>
       </c>
-      <c r="B1079" s="28" t="inlineStr">
+      <c r="B1079" s="31" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1079" s="28" t="inlineStr"/>
+      <c r="C1079" s="31" t="inlineStr"/>
       <c r="D1079" s="29" t="inlineStr"/>
-      <c r="E1079" s="28">
+      <c r="E1079" s="31">
         <f>IF(C1079&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1080">
-      <c r="A1080" s="26" t="inlineStr">
+      <c r="A1080" s="30" t="inlineStr">
         <is>
           <t>Чипсы Принглс 165г/19 Паприка</t>
         </is>
       </c>
-      <c r="B1080" s="26" t="inlineStr">
+      <c r="B1080" s="30" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1080" s="26" t="inlineStr"/>
+      <c r="C1080" s="30" t="inlineStr"/>
       <c r="D1080" s="27" t="inlineStr"/>
-      <c r="E1080" s="26">
+      <c r="E1080" s="30">
         <f>IF(C1080&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1081">
-      <c r="A1081" s="28" t="inlineStr">
+      <c r="A1081" s="31" t="inlineStr">
         <is>
           <t>Чипсы Принглс 165г/19 Сметана Лук</t>
         </is>
       </c>
-      <c r="B1081" s="28" t="inlineStr">
+      <c r="B1081" s="31" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1081" s="28" t="inlineStr"/>
+      <c r="C1081" s="31" t="inlineStr"/>
       <c r="D1081" s="29" t="inlineStr"/>
-      <c r="E1081" s="28">
+      <c r="E1081" s="31">
         <f>IF(C1081&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1082">
-      <c r="A1082" s="26" t="inlineStr">
+      <c r="A1082" s="30" t="inlineStr">
         <is>
           <t>Чипсы Принглс 40г/12 Паприка</t>
         </is>
       </c>
-      <c r="B1082" s="26" t="inlineStr">
+      <c r="B1082" s="30" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1082" s="26" t="inlineStr"/>
+      <c r="C1082" s="30" t="inlineStr"/>
       <c r="D1082" s="27" t="inlineStr"/>
-      <c r="E1082" s="26">
+      <c r="E1082" s="30">
         <f>IF(C1082&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1083">
-      <c r="A1083" s="28" t="inlineStr">
+      <c r="A1083" s="31" t="inlineStr">
         <is>
           <t>Чипсы Принглс 40г/12 Сметана Лук</t>
         </is>
       </c>
-      <c r="B1083" s="28" t="inlineStr">
+      <c r="B1083" s="31" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1083" s="28" t="inlineStr"/>
+      <c r="C1083" s="31" t="inlineStr"/>
       <c r="D1083" s="29" t="inlineStr"/>
-      <c r="E1083" s="28">
+      <c r="E1083" s="31">
         <f>IF(C1083&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1084">
-      <c r="A1084" s="26" t="inlineStr">
+      <c r="A1084" s="30" t="inlineStr">
         <is>
           <t>Чипсы Принглс 40г/12 Техасский BBQ</t>
         </is>
       </c>
-      <c r="B1084" s="26" t="inlineStr">
+      <c r="B1084" s="30" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1084" s="26" t="inlineStr"/>
+      <c r="C1084" s="30" t="inlineStr"/>
       <c r="D1084" s="27" t="inlineStr"/>
-      <c r="E1084" s="26">
+      <c r="E1084" s="30">
         <f>IF(C1084&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1085">
-      <c r="A1085" s="28" t="inlineStr">
+      <c r="A1085" s="31" t="inlineStr">
         <is>
           <t>Чипсы Принглс Оригинал 40г/12</t>
         </is>
       </c>
-      <c r="B1085" s="28" t="inlineStr">
+      <c r="B1085" s="31" t="inlineStr">
         <is>
           <t>Снэки</t>
         </is>
       </c>
-      <c r="C1085" s="28" t="inlineStr"/>
+      <c r="C1085" s="31" t="inlineStr"/>
       <c r="D1085" s="29" t="inlineStr"/>
-      <c r="E1085" s="28">
+      <c r="E1085" s="31">
         <f>IF(C1085&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1086">
-      <c r="A1086" s="26" t="inlineStr">
+      <c r="A1086" s="30" t="inlineStr">
         <is>
           <t>Чай Ахмад 100пак/8шт черн. English Breakfast (англ. завтрак)</t>
         </is>
       </c>
-      <c r="B1086" s="26" t="inlineStr">
+      <c r="B1086" s="30" t="inlineStr">
         <is>
           <t>Соусы и специи</t>
         </is>
       </c>
-      <c r="C1086" s="26" t="inlineStr"/>
+      <c r="C1086" s="30" t="inlineStr"/>
       <c r="D1086" s="27" t="inlineStr"/>
-      <c r="E1086" s="26">
+      <c r="E1086" s="30">
         <f>IF(C1086&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1087">
-      <c r="A1087" s="28" t="inlineStr">
+      <c r="A1087" s="31" t="inlineStr">
         <is>
           <t>Стоевъ Кетчуп "Сеньор Помидор" Острый п/бут 850 мл./8</t>
         </is>
       </c>
-      <c r="B1087" s="28" t="inlineStr">
+      <c r="B1087" s="31" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1087" s="28" t="inlineStr"/>
+      <c r="C1087" s="31" t="inlineStr"/>
       <c r="D1087" s="29" t="inlineStr"/>
-      <c r="E1087" s="28">
+      <c r="E1087" s="31">
         <f>IF(C1087&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1088">
-      <c r="A1088" s="26" t="inlineStr">
+      <c r="A1088" s="30" t="inlineStr">
         <is>
           <t>Стоевъ Перец Халапеньо зеленый нарезаный с/б 350г/12</t>
         </is>
       </c>
-      <c r="B1088" s="26" t="inlineStr">
+      <c r="B1088" s="30" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1088" s="26" t="inlineStr"/>
+      <c r="C1088" s="30" t="inlineStr"/>
       <c r="D1088" s="27" t="inlineStr"/>
-      <c r="E1088" s="26">
+      <c r="E1088" s="30">
         <f>IF(C1088&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1089">
-      <c r="A1089" s="28" t="inlineStr">
+      <c r="A1089" s="31" t="inlineStr">
         <is>
           <t>Стоевъ Приправа Лимонная кислота zip-lock 50 г./30</t>
         </is>
       </c>
-      <c r="B1089" s="28" t="inlineStr">
+      <c r="B1089" s="31" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1089" s="28" t="inlineStr"/>
+      <c r="C1089" s="31" t="inlineStr"/>
       <c r="D1089" s="29" t="inlineStr"/>
-      <c r="E1089" s="28">
+      <c r="E1089" s="31">
         <f>IF(C1089&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1090">
-      <c r="A1090" s="26" t="inlineStr">
+      <c r="A1090" s="30" t="inlineStr">
         <is>
           <t>Стоевъ Приправа Паприка дробленая  zip-lock 30 г./30</t>
         </is>
       </c>
-      <c r="B1090" s="26" t="inlineStr">
+      <c r="B1090" s="30" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1090" s="26" t="inlineStr"/>
+      <c r="C1090" s="30" t="inlineStr"/>
       <c r="D1090" s="27" t="inlineStr"/>
-      <c r="E1090" s="26">
+      <c r="E1090" s="30">
         <f>IF(C1090&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1091">
-      <c r="A1091" s="28" t="inlineStr">
+      <c r="A1091" s="31" t="inlineStr">
         <is>
           <t>Стоевъ Приправа Петрушка zip-lock 10г./30</t>
         </is>
       </c>
-      <c r="B1091" s="28" t="inlineStr">
+      <c r="B1091" s="31" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1091" s="28" t="inlineStr"/>
+      <c r="C1091" s="31" t="inlineStr"/>
       <c r="D1091" s="29" t="inlineStr"/>
-      <c r="E1091" s="28">
+      <c r="E1091" s="31">
         <f>IF(C1091&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1092">
-      <c r="A1092" s="26" t="inlineStr">
+      <c r="A1092" s="30" t="inlineStr">
         <is>
           <t>Стоевъ Соленья Чеснок маринованный  с/б 190 мл/8</t>
         </is>
       </c>
-      <c r="B1092" s="26" t="inlineStr">
+      <c r="B1092" s="30" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1092" s="26" t="inlineStr"/>
+      <c r="C1092" s="30" t="inlineStr"/>
       <c r="D1092" s="27" t="inlineStr"/>
-      <c r="E1092" s="26">
+      <c r="E1092" s="30">
         <f>IF(C1092&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1093">
-      <c r="A1093" s="28" t="inlineStr">
+      <c r="A1093" s="31" t="inlineStr">
         <is>
           <t>Холодный чай Липтон лимон 0.5/12</t>
         </is>
       </c>
-      <c r="B1093" s="28" t="inlineStr">
+      <c r="B1093" s="31" t="inlineStr">
         <is>
           <t>Стоевъ и Сэнсой</t>
         </is>
       </c>
-      <c r="C1093" s="28" t="inlineStr"/>
+      <c r="C1093" s="31" t="inlineStr"/>
       <c r="D1093" s="29" t="inlineStr"/>
-      <c r="E1093" s="28">
+      <c r="E1093" s="31">
         <f>IF(C1093&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1094">
-      <c r="A1094" s="26" t="inlineStr">
+      <c r="A1094" s="30" t="inlineStr">
         <is>
           <t>Кофе Жокей молотый Классический 450г/12шт</t>
         </is>
       </c>
-      <c r="B1094" s="26" t="inlineStr">
+      <c r="B1094" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1094" s="26" t="inlineStr"/>
+      <c r="C1094" s="30" t="inlineStr"/>
       <c r="D1094" s="27" t="inlineStr"/>
-      <c r="E1094" s="26">
+      <c r="E1094" s="30">
         <f>IF(C1094&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1095">
-      <c r="A1095" s="28" t="inlineStr">
+      <c r="A1095" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый Голд м/у 100г/10шт</t>
         </is>
       </c>
-      <c r="B1095" s="28" t="inlineStr">
+      <c r="B1095" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1095" s="28" t="inlineStr"/>
+      <c r="C1095" s="31" t="inlineStr"/>
       <c r="D1095" s="29" t="inlineStr"/>
-      <c r="E1095" s="28">
+      <c r="E1095" s="31">
         <f>IF(C1095&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1096">
-      <c r="A1096" s="26" t="inlineStr">
+      <c r="A1096" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый Джезва 90г/20шт</t>
         </is>
       </c>
-      <c r="B1096" s="26" t="inlineStr">
+      <c r="B1096" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1096" s="26" t="inlineStr"/>
+      <c r="C1096" s="30" t="inlineStr"/>
       <c r="D1096" s="27" t="inlineStr"/>
-      <c r="E1096" s="26">
+      <c r="E1096" s="30">
         <f>IF(C1096&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1097">
-      <c r="A1097" s="28" t="inlineStr">
+      <c r="A1097" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый ирл. сливки 150г/12шт</t>
         </is>
       </c>
-      <c r="B1097" s="28" t="inlineStr">
+      <c r="B1097" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1097" s="28" t="inlineStr"/>
+      <c r="C1097" s="31" t="inlineStr"/>
       <c r="D1097" s="29" t="inlineStr"/>
-      <c r="E1097" s="28">
+      <c r="E1097" s="31">
         <f>IF(C1097&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1098">
-      <c r="A1098" s="26" t="inlineStr">
+      <c r="A1098" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый ирл. сливки 70г/12шт</t>
         </is>
       </c>
-      <c r="B1098" s="26" t="inlineStr">
+      <c r="B1098" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1098" s="26" t="inlineStr"/>
+      <c r="C1098" s="30" t="inlineStr"/>
       <c r="D1098" s="27" t="inlineStr"/>
-      <c r="E1098" s="26">
+      <c r="E1098" s="30">
         <f>IF(C1098&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1099">
-      <c r="A1099" s="28" t="inlineStr">
+      <c r="A1099" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый карамель TOFEE  70г/12шт</t>
         </is>
       </c>
-      <c r="B1099" s="28" t="inlineStr">
+      <c r="B1099" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1099" s="28" t="inlineStr"/>
+      <c r="C1099" s="31" t="inlineStr"/>
       <c r="D1099" s="29" t="inlineStr"/>
-      <c r="E1099" s="28">
+      <c r="E1099" s="31">
         <f>IF(C1099&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1100">
-      <c r="A1100" s="26" t="inlineStr">
+      <c r="A1100" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый карамель TOFEE 150г/12шт</t>
         </is>
       </c>
-      <c r="B1100" s="26" t="inlineStr">
+      <c r="B1100" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1100" s="26" t="inlineStr"/>
+      <c r="C1100" s="30" t="inlineStr"/>
       <c r="D1100" s="27" t="inlineStr"/>
-      <c r="E1100" s="26">
+      <c r="E1100" s="30">
         <f>IF(C1100&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1101">
-      <c r="A1101" s="28" t="inlineStr">
+      <c r="A1101" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый Классик в/с (для турки) 100г/50шт</t>
         </is>
       </c>
-      <c r="B1101" s="28" t="inlineStr">
+      <c r="B1101" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1101" s="28" t="inlineStr"/>
+      <c r="C1101" s="31" t="inlineStr"/>
       <c r="D1101" s="29" t="inlineStr"/>
-      <c r="E1101" s="28">
+      <c r="E1101" s="31">
         <f>IF(C1101&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1102">
-      <c r="A1102" s="26" t="inlineStr">
+      <c r="A1102" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый Оригинал ст/б 100г/12шт</t>
         </is>
       </c>
-      <c r="B1102" s="26" t="inlineStr">
+      <c r="B1102" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1102" s="26" t="inlineStr"/>
+      <c r="C1102" s="30" t="inlineStr"/>
       <c r="D1102" s="27" t="inlineStr"/>
-      <c r="E1102" s="26">
+      <c r="E1102" s="30">
         <f>IF(C1102&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1103">
-      <c r="A1103" s="28" t="inlineStr">
+      <c r="A1103" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый принц (для турки) 100г/50шт</t>
         </is>
       </c>
-      <c r="B1103" s="28" t="inlineStr">
+      <c r="B1103" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1103" s="28" t="inlineStr"/>
+      <c r="C1103" s="31" t="inlineStr"/>
       <c r="D1103" s="29" t="inlineStr"/>
-      <c r="E1103" s="28">
+      <c r="E1103" s="31">
         <f>IF(C1103&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1104">
-      <c r="A1104" s="26" t="inlineStr">
+      <c r="A1104" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый Принц Оригинал (для турки) 100г/50шт</t>
         </is>
       </c>
-      <c r="B1104" s="26" t="inlineStr">
+      <c r="B1104" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1104" s="26" t="inlineStr"/>
+      <c r="C1104" s="30" t="inlineStr"/>
       <c r="D1104" s="27" t="inlineStr"/>
-      <c r="E1104" s="26">
+      <c r="E1104" s="30">
         <f>IF(C1104&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1105">
-      <c r="A1105" s="28" t="inlineStr">
+      <c r="A1105" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый шоколад Choco Brownie 70г/12шт</t>
         </is>
       </c>
-      <c r="B1105" s="28" t="inlineStr">
+      <c r="B1105" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1105" s="28" t="inlineStr"/>
+      <c r="C1105" s="31" t="inlineStr"/>
       <c r="D1105" s="29" t="inlineStr"/>
-      <c r="E1105" s="28">
+      <c r="E1105" s="31">
         <f>IF(C1105&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1106">
-      <c r="A1106" s="26" t="inlineStr">
+      <c r="A1106" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый шоколад Брауни 150г/12шт</t>
         </is>
       </c>
-      <c r="B1106" s="26" t="inlineStr">
+      <c r="B1106" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1106" s="26" t="inlineStr"/>
+      <c r="C1106" s="30" t="inlineStr"/>
       <c r="D1106" s="27" t="inlineStr"/>
-      <c r="E1106" s="26">
+      <c r="E1106" s="30">
         <f>IF(C1106&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1107">
-      <c r="A1107" s="28" t="inlineStr">
+      <c r="A1107" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо молотый эксклюзив м/у 100г/10шт</t>
         </is>
       </c>
-      <c r="B1107" s="28" t="inlineStr">
+      <c r="B1107" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1107" s="28" t="inlineStr"/>
+      <c r="C1107" s="31" t="inlineStr"/>
       <c r="D1107" s="29" t="inlineStr"/>
-      <c r="E1107" s="28">
+      <c r="E1107" s="31">
         <f>IF(C1107&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1108">
-      <c r="A1108" s="26" t="inlineStr">
+      <c r="A1108" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо сублимированный  Экстра ст/б 100г/12</t>
         </is>
       </c>
-      <c r="B1108" s="26" t="inlineStr">
+      <c r="B1108" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1108" s="26" t="inlineStr"/>
+      <c r="C1108" s="30" t="inlineStr"/>
       <c r="D1108" s="27" t="inlineStr"/>
-      <c r="E1108" s="26">
+      <c r="E1108" s="30">
         <f>IF(C1108&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1109">
-      <c r="A1109" s="28" t="inlineStr">
+      <c r="A1109" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо сублимированный Голд ст/б 100г/12шт</t>
         </is>
       </c>
-      <c r="B1109" s="28" t="inlineStr">
+      <c r="B1109" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1109" s="28" t="inlineStr"/>
+      <c r="C1109" s="31" t="inlineStr"/>
       <c r="D1109" s="29" t="inlineStr"/>
-      <c r="E1109" s="28">
+      <c r="E1109" s="31">
         <f>IF(C1109&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1110">
-      <c r="A1110" s="26" t="inlineStr">
+      <c r="A1110" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо сублимированный Классик ст/б 100г/12шт</t>
         </is>
       </c>
-      <c r="B1110" s="26" t="inlineStr">
+      <c r="B1110" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1110" s="26" t="inlineStr"/>
+      <c r="C1110" s="30" t="inlineStr"/>
       <c r="D1110" s="27" t="inlineStr"/>
-      <c r="E1110" s="26">
+      <c r="E1110" s="30">
         <f>IF(C1110&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1111">
-      <c r="A1111" s="28" t="inlineStr">
+      <c r="A1111" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо сублимированный эксклюзив ст/б 100г/12шт</t>
         </is>
       </c>
-      <c r="B1111" s="28" t="inlineStr">
+      <c r="B1111" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1111" s="28" t="inlineStr"/>
+      <c r="C1111" s="31" t="inlineStr"/>
       <c r="D1111" s="29" t="inlineStr"/>
-      <c r="E1111" s="28">
+      <c r="E1111" s="31">
         <f>IF(C1111&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1112">
-      <c r="A1112" s="26" t="inlineStr">
+      <c r="A1112" s="30" t="inlineStr">
         <is>
           <t>Кофе Лебо Экстра м/у 100г/10</t>
         </is>
       </c>
-      <c r="B1112" s="26" t="inlineStr">
+      <c r="B1112" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1112" s="26" t="inlineStr"/>
+      <c r="C1112" s="30" t="inlineStr"/>
       <c r="D1112" s="27" t="inlineStr"/>
-      <c r="E1112" s="26">
+      <c r="E1112" s="30">
         <f>IF(C1112&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1113">
-      <c r="A1113" s="28" t="inlineStr">
+      <c r="A1113" s="31" t="inlineStr">
         <is>
           <t>Кофе Лебо Экстра м/у 170г/6</t>
         </is>
       </c>
-      <c r="B1113" s="28" t="inlineStr">
+      <c r="B1113" s="31" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1113" s="28" t="inlineStr"/>
+      <c r="C1113" s="31" t="inlineStr"/>
       <c r="D1113" s="29" t="inlineStr"/>
-      <c r="E1113" s="28">
+      <c r="E1113" s="31">
         <f>IF(C1113&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1114">
-      <c r="A1114" s="26" t="inlineStr">
+      <c r="A1114" s="30" t="inlineStr">
         <is>
           <t>Кофе МакКофе 3в1 20г/25шт (40)</t>
         </is>
       </c>
-      <c r="B1114" s="26" t="inlineStr">
+      <c r="B1114" s="30" t="inlineStr">
         <is>
           <t>Чай и кофе</t>
         </is>
       </c>
-      <c r="C1114" s="26" t="inlineStr"/>
+      <c r="C1114" s="30" t="inlineStr"/>
       <c r="D1114" s="27" t="inlineStr"/>
-      <c r="E1114" s="26">
+      <c r="E1114" s="30">
         <f>IF(C1114&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1115">
-      <c r="A1115" s="28" t="inlineStr">
+      <c r="A1115" s="31" t="inlineStr">
         <is>
           <t>Энергетик Торнадо 0.45л/12 ж/б Макс Оригинал</t>
         </is>
       </c>
-      <c r="B1115" s="28" t="inlineStr">
+      <c r="B1115" s="31" t="inlineStr">
         <is>
           <t>Энергетики</t>
         </is>
       </c>
-      <c r="C1115" s="28" t="inlineStr"/>
+      <c r="C1115" s="31" t="inlineStr"/>
       <c r="D1115" s="29" t="inlineStr"/>
-      <c r="E1115" s="28">
+      <c r="E1115" s="31">
         <f>IF(C1115&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1116">
-      <c r="A1116" s="26" t="inlineStr">
+      <c r="A1116" s="30" t="inlineStr">
         <is>
           <t>Энергетик Флеш Энерджи 0,45л/24 ж/б Апельсин</t>
         </is>
       </c>
-      <c r="B1116" s="26" t="inlineStr">
+      <c r="B1116" s="30" t="inlineStr">
         <is>
           <t>Энергетики</t>
         </is>
       </c>
-      <c r="C1116" s="26" t="inlineStr"/>
+      <c r="C1116" s="30" t="inlineStr"/>
       <c r="D1116" s="27" t="inlineStr"/>
-      <c r="E1116" s="26">
+      <c r="E1116" s="30">
         <f>IF(C1116&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>
     <row r="1117">
-      <c r="A1117" s="28" t="inlineStr">
+      <c r="A1117" s="31" t="inlineStr">
         <is>
           <t>Энергетик Флеш Энерджи 0,45л/24 ж/б Манго/Ананас</t>
         </is>
       </c>
-      <c r="B1117" s="28" t="inlineStr">
+      <c r="B1117" s="31" t="inlineStr">
         <is>
           <t>Энергетики</t>
         </is>
       </c>
-      <c r="C1117" s="28" t="inlineStr"/>
+      <c r="C1117" s="31" t="inlineStr"/>
       <c r="D1117" s="29" t="inlineStr"/>
-      <c r="E1117" s="28">
+      <c r="E1117" s="31">
         <f>IF(C1117&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
@@ -28575,6 +28575,237 @@
       <c r="D1298" s="27" t="inlineStr"/>
       <c r="E1298" s="30">
         <f>IF(C1298&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Апельсин 1л/12</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/707.webp</t>
+        </is>
+      </c>
+      <c r="E1299">
+        <f>IF(C1299&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Кола 0.5/24</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/716.jpg</t>
+        </is>
+      </c>
+      <c r="E1300">
+        <f>IF(C1300&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Кола 1л/12 БЕЗ САХАРА</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/718.jpg</t>
+        </is>
+      </c>
+      <c r="E1301">
+        <f>IF(C1301&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Палпи апельсин 0.45/12</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/699.webp</t>
+        </is>
+      </c>
+      <c r="E1302">
+        <f>IF(C1302&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Палпи апельсин 0.9/12</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/699.webp</t>
+        </is>
+      </c>
+      <c r="E1303">
+        <f>IF(C1303&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Добрый СОК 1л/12 Апельсин и мандарин</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/710.jpg</t>
+        </is>
+      </c>
+      <c r="E1304">
+        <f>IF(C1304&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>Добрый СОК 1л/12 Мультифрукт</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/dobry_multifrukt.jpg</t>
+        </is>
+      </c>
+      <c r="E1305">
+        <f>IF(C1305&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>Добрый СОК 1л/12 Персик</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/dobry_persik.jpg</t>
+        </is>
+      </c>
+      <c r="E1306">
+        <f>IF(C1306&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Добрый СОК 1л/12 Яблоко</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/705.webp</t>
+        </is>
+      </c>
+      <c r="E1307">
+        <f>IF(C1307&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Добрый СОК 2л/6 Мультифрукт</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/711.webp</t>
+        </is>
+      </c>
+      <c r="E1308">
+        <f>IF(C1308&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Добрый СОК 2л/6 Яблоко</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/713.webp</t>
+        </is>
+      </c>
+      <c r="E1309">
+        <f>IF(C1309&lt;&gt;"","✅","❌")</f>
         <v/>
       </c>
     </row>

--- a/photo_manual.xlsx
+++ b/photo_manual.xlsx
@@ -1219,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1309"/>
+  <dimension ref="A1:E1312"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -28807,6 +28807,42 @@
       <c r="E1309">
         <f>IF(C1309&lt;&gt;"","✅","❌")</f>
         <v/>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Киви-Виноград 0.33/12Ж/Б</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/4118.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Кола 0.33/12 ж\б Без сахара</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/3479.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Добрый ВОДА Лимон-Лайм 0.33/12 Ж/Б</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/4866.jpg</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/photo_manual.xlsx
+++ b/photo_manual.xlsx
@@ -1219,7 +1219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1312"/>
+  <dimension ref="A1:E1318"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -28843,6 +28843,132 @@
         <is>
           <t>file:///C:/catalog/photos/4866.jpg</t>
         </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>Вода мин. Газ. Аква Драйв Брейн Баланс Пэт 0.45л/12шт зеленый</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/Screenshot_173.png</t>
+        </is>
+      </c>
+      <c r="E1313">
+        <f>IF(C1313&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Вода мин.Газ. Аква Драйв Спорт Пэт 0.45л/12шт синий</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/Screenshot_172.png</t>
+        </is>
+      </c>
+      <c r="E1314">
+        <f>IF(C1314&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Вода мин.Газ. Аква Драйв Фитнес Пэт 0.45л/12шт розовый</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/voda_min_akva_drayv_fitnes_pet_045l_12sht_rozovyy.webp</t>
+        </is>
+      </c>
+      <c r="E1315">
+        <f>IF(C1315&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Добрый СОК 1л/12 Томат</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/706.webp</t>
+        </is>
+      </c>
+      <c r="E1316">
+        <f>IF(C1316&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Добрый Моя Семья Яблоко 0.2/27</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/5352.jpg</t>
+        </is>
+      </c>
+      <c r="E1317">
+        <f>IF(C1317&lt;&gt;"","✅","❌")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Добрый Моя Семья ягода 0.2/27</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Напитки</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>file:///C:/catalog/photos/5355.png</t>
+        </is>
+      </c>
+      <c r="E1318">
+        <f>IF(C1318&lt;&gt;"","✅","❌")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
